--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q17">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>6.88</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC11">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU23"/>
+  <dimension ref="A1:AU25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G2">
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-10-29 10:15:00</t>
+          <t>2026-10-29 10:00:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G3">
@@ -794,7 +794,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-10-29 10:30:00</t>
+          <t>2026-10-29 10:15:00</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G5">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-10-29 11:00:00</t>
+          <t>2026-10-29 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-10-29 11:10:00</t>
+          <t>2026-10-29 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-10-29 11:35:00</t>
+          <t>2026-10-29 11:10:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-10-29 12:00:00</t>
+          <t>2026-10-29 11:35:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-10-29 13:30:00</t>
+          <t>2026-10-29 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>6.88</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-10-29 14:00:00</t>
+          <t>2026-10-29 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.53</v>
+        <v>2.85</v>
       </c>
       <c r="O12">
-        <v>4.4</v>
+        <v>3.34</v>
       </c>
       <c r="P12">
-        <v>5.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-10-29 14:30:00</t>
+          <t>2026-10-29 13:30:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="P13">
-        <v>4.06</v>
+        <v>6.88</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AB13">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AC13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-10-29 14:30:00</t>
+          <t>2026-10-29 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5.13</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-29 15:00:00</t>
+          <t>2026-10-29 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-10-29 15:00:00</t>
+          <t>2026-10-29 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-10-29 16:45:00</t>
+          <t>2026-10-29 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.4</v>
+        <v>3.22</v>
       </c>
       <c r="O19">
-        <v>3.69</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-10-29 16:45:00</t>
+          <t>2026-10-29 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-29 17:00:00</t>
+          <t>2026-10-29 16:45:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O21">
-        <v>3.45</v>
+        <v>3.69</v>
       </c>
       <c r="P21">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-10-29 19:30:00</t>
+          <t>2026-10-29 16:45:00</t>
         </is>
       </c>
     </row>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-29 20:00:00</t>
+          <t>2026-10-29 17:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,156 +4011,482 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>2.48</v>
+      </c>
+      <c r="O23">
+        <v>3.45</v>
+      </c>
+      <c r="P23">
+        <v>2.87</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>1.95</v>
+      </c>
+      <c r="AB23">
+        <v>1.9</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>3.69</v>
+      </c>
+      <c r="O24">
+        <v>3.59</v>
+      </c>
+      <c r="P24">
+        <v>2.03</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>1.88</v>
+      </c>
+      <c r="AB24">
+        <v>1.98</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-10-29 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Grêmio</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Atlético PR</t>
         </is>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23" t="inlineStr">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N23">
+      <c r="N25">
         <v>2.2</v>
       </c>
-      <c r="O23">
+      <c r="O25">
         <v>3.39</v>
       </c>
-      <c r="P23">
+      <c r="P25">
         <v>3.43</v>
       </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>0</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
-      </c>
-      <c r="X23">
-        <v>0</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>0</v>
-      </c>
-      <c r="AA23">
-        <v>0</v>
-      </c>
-      <c r="AB23">
-        <v>0</v>
-      </c>
-      <c r="AC23">
-        <v>0</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>0</v>
-      </c>
-      <c r="AK23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>-1</v>
-      </c>
-      <c r="AN23">
-        <v>-1</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>-1</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
         <is>
           <t>2026-10-29 21:30:00</t>
         </is>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1622,55 +1622,55 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>2.2</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,34 +2437,34 @@
         <v>6.88</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA13">
         <v>1.94</v>
@@ -2473,19 +2473,19 @@
         <v>1.89</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>4.06</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="AA15">
         <v>1.81</v>
@@ -2799,19 +2799,19 @@
         <v>2</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="O18">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P19">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>3.06</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -4067,34 +4067,34 @@
         <v>2.87</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AA23">
         <v>1.95</v>
@@ -4103,19 +4103,19 @@
         <v>1.9</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>2.03</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="AA24">
         <v>1.88</v>
@@ -4266,19 +4266,19 @@
         <v>1.98</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>3.43</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2926,55 +2926,55 @@
         <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>10.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1779,16 +1779,16 @@
         <v>2.1</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="S9">
         <v>1.34</v>
@@ -1797,7 +1797,7 @@
         <v>2.8</v>
       </c>
       <c r="U9">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="V9">
         <v>1.38</v>
@@ -1812,19 +1812,19 @@
         <v>1.27</v>
       </c>
       <c r="Z9">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="AA9">
         <v>1.88</v>
       </c>
       <c r="AB9">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AC9">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE9">
         <v>1.12</v>
@@ -1849,7 +1849,7 @@
         <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2600,10 +2600,10 @@
         <v>5.13</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2612,37 +2612,37 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X14">
         <v>0</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>2.17</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,10 +3415,10 @@
         <v>2.03</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -3427,37 +3427,37 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X19">
         <v>0</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF19">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1821,10 +1821,10 @@
         <v>1.88</v>
       </c>
       <c r="AC9">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AD9">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE9">
         <v>1.12</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="P15">
-        <v>4.06</v>
+        <v>3.96</v>
       </c>
       <c r="Q15">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="R15">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
+        <v>1.24</v>
+      </c>
+      <c r="T15">
+        <v>3.65</v>
+      </c>
+      <c r="U15">
+        <v>2.21</v>
+      </c>
+      <c r="V15">
+        <v>1.64</v>
+      </c>
+      <c r="W15">
+        <v>1.16</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.13</v>
+      </c>
+      <c r="Z15">
+        <v>5.24</v>
+      </c>
+      <c r="AA15">
+        <v>1.48</v>
+      </c>
+      <c r="AB15">
+        <v>2.4</v>
+      </c>
+      <c r="AC15">
+        <v>2.15</v>
+      </c>
+      <c r="AD15">
+        <v>1.64</v>
+      </c>
+      <c r="AE15">
         <v>1.26</v>
       </c>
-      <c r="T15">
-        <v>3.48</v>
-      </c>
-      <c r="U15">
-        <v>2.3</v>
-      </c>
-      <c r="V15">
-        <v>1.6</v>
-      </c>
-      <c r="W15">
-        <v>1.14</v>
-      </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>1.15</v>
-      </c>
-      <c r="Z15">
-        <v>4.92</v>
-      </c>
-      <c r="AA15">
-        <v>1.81</v>
-      </c>
-      <c r="AB15">
-        <v>2</v>
-      </c>
-      <c r="AC15">
-        <v>2.4</v>
-      </c>
-      <c r="AD15">
-        <v>1.58</v>
-      </c>
-      <c r="AE15">
-        <v>1.23</v>
-      </c>
       <c r="AF15">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AG15">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK15">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="O16">
-        <v>6.13</v>
+        <v>5.4</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q16">
         <v>6.8</v>
@@ -2956,13 +2956,13 @@
         <v>7.25</v>
       </c>
       <c r="AA16">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AC16">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AD16">
         <v>1.76</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="O17">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="P17">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q17">
         <v>1.52</v>
@@ -3732,65 +3732,65 @@
         </is>
       </c>
       <c r="N21">
+        <v>2.09</v>
+      </c>
+      <c r="O21">
+        <v>3.6</v>
+      </c>
+      <c r="P21">
+        <v>3.05</v>
+      </c>
+      <c r="Q21">
+        <v>2.59</v>
+      </c>
+      <c r="R21">
+        <v>2.3</v>
+      </c>
+      <c r="S21">
+        <v>1.25</v>
+      </c>
+      <c r="T21">
+        <v>3.6</v>
+      </c>
+      <c r="U21">
+        <v>2.25</v>
+      </c>
+      <c r="V21">
+        <v>1.57</v>
+      </c>
+      <c r="W21">
+        <v>1.11</v>
+      </c>
+      <c r="X21">
+        <v>1.01</v>
+      </c>
+      <c r="Y21">
+        <v>1.2</v>
+      </c>
+      <c r="Z21">
+        <v>4.36</v>
+      </c>
+      <c r="AA21">
+        <v>1.6</v>
+      </c>
+      <c r="AB21">
+        <v>2.17</v>
+      </c>
+      <c r="AC21">
+        <v>2.56</v>
+      </c>
+      <c r="AD21">
+        <v>1.52</v>
+      </c>
+      <c r="AE21">
+        <v>1.15</v>
+      </c>
+      <c r="AF21">
+        <v>1.5</v>
+      </c>
+      <c r="AG21">
         <v>2.4</v>
       </c>
-      <c r="O21">
-        <v>3.69</v>
-      </c>
-      <c r="P21">
-        <v>3.06</v>
-      </c>
-      <c r="Q21">
-        <v>2.79</v>
-      </c>
-      <c r="R21">
-        <v>2.18</v>
-      </c>
-      <c r="S21">
-        <v>1.33</v>
-      </c>
-      <c r="T21">
-        <v>3.12</v>
-      </c>
-      <c r="U21">
-        <v>2.51</v>
-      </c>
-      <c r="V21">
-        <v>1.49</v>
-      </c>
-      <c r="W21">
-        <v>1.09</v>
-      </c>
-      <c r="X21">
-        <v>1</v>
-      </c>
-      <c r="Y21">
-        <v>1.22</v>
-      </c>
-      <c r="Z21">
-        <v>4.06</v>
-      </c>
-      <c r="AA21">
-        <v>1.72</v>
-      </c>
-      <c r="AB21">
-        <v>2.14</v>
-      </c>
-      <c r="AC21">
-        <v>2.74</v>
-      </c>
-      <c r="AD21">
-        <v>1.45</v>
-      </c>
-      <c r="AE21">
-        <v>1.17</v>
-      </c>
-      <c r="AF21">
-        <v>1.57</v>
-      </c>
-      <c r="AG21">
-        <v>2.25</v>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
         <v>1.64</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2271,58 +2271,58 @@
         <v>3.34</v>
       </c>
       <c r="P12">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q12">
         <v>3.28</v>
       </c>
       <c r="R12">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="U12">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AA12">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AB12">
         <v>2</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.69</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF12">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AG12">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P14">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="R14">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U14">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W14">
         <v>1.18</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z14">
-        <v>4.85</v>
+        <v>5.35</v>
       </c>
       <c r="AA14">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AB14">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="AC14">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AD14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AE14">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="O15">
-        <v>3.68</v>
+        <v>4.35</v>
       </c>
       <c r="P15">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="U15">
-        <v>2.21</v>
+        <v>2.28</v>
       </c>
       <c r="V15">
         <v>1.64</v>
       </c>
       <c r="W15">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z15">
-        <v>5.24</v>
+        <v>5.51</v>
       </c>
       <c r="AA15">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC15">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AD15">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG15">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK15">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="R18">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T18">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="V18">
         <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,7 +3282,7 @@
         <v>3.28</v>
       </c>
       <c r="AA18">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB18">
         <v>1.86</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AK18">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Q19">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="R19">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U19">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z19">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA19">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB19">
         <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="AD19">
         <v>1.43</v>
       </c>
       <c r="AE19">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="O21">
         <v>3.6</v>
@@ -3741,7 +3741,7 @@
         <v>3.05</v>
       </c>
       <c r="Q21">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="R21">
         <v>2.3</v>
@@ -3771,10 +3771,10 @@
         <v>4.36</v>
       </c>
       <c r="AA21">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AB21">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AC21">
         <v>2.56</v>
@@ -3786,10 +3786,10 @@
         <v>1.15</v>
       </c>
       <c r="AF21">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AG21">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -4100,7 +4100,7 @@
         <v>1.95</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
         <v>3.26</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="O24">
-        <v>3.59</v>
+        <v>3.48</v>
       </c>
       <c r="P24">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q24">
         <v>4</v>
@@ -4248,7 +4248,7 @@
         <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
         <v>1</v>
@@ -4260,10 +4260,10 @@
         <v>3.53</v>
       </c>
       <c r="AA24">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB24">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
         <v>2.99</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.73</v>
+        <v>1.31</v>
       </c>
       <c r="AK24">
         <v>1.31</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1450,55 +1450,55 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="O7">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q7">
         <v>6</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T7">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z7">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="AA7">
         <v>2.02</v>
       </c>
       <c r="AB7">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC7">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="AD7">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
         <v>1.05</v>
@@ -1667,7 +1667,7 @@
         <v>1.27</v>
       </c>
       <c r="AF8">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
         <v>2.04</v>
@@ -1821,10 +1821,10 @@
         <v>1.88</v>
       </c>
       <c r="AC9">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE9">
         <v>1.12</v>
@@ -2268,10 +2268,10 @@
         <v>2.85</v>
       </c>
       <c r="O12">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
         <v>3.28</v>
@@ -2304,7 +2304,7 @@
         <v>3.88</v>
       </c>
       <c r="AA12">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
         <v>2</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O13">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P13">
-        <v>6.88</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R13">
         <v>2.25</v>
@@ -2449,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="U13">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V13">
         <v>1.44</v>
@@ -2467,10 +2467,10 @@
         <v>3.34</v>
       </c>
       <c r="AA13">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB13">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2482,10 +2482,10 @@
         <v>1.08</v>
       </c>
       <c r="AF13">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2953,7 +2953,7 @@
         <v>1.07</v>
       </c>
       <c r="Z16">
-        <v>7.25</v>
+        <v>6.73</v>
       </c>
       <c r="AA16">
         <v>1.4</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3608,7 +3608,7 @@
         <v>3.42</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB20">
         <v>1.7</v>
@@ -3642,7 +3642,7 @@
         <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL20">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="Q25">
         <v>3.02</v>
@@ -4423,10 +4423,10 @@
         <v>2.97</v>
       </c>
       <c r="AA25">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB25">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AC25">
         <v>3.94</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1779,7 +1779,7 @@
         <v>2.1</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
         <v>3.1</v>
@@ -3089,7 +3089,7 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R17">
         <v>2.93</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2268,7 +2268,7 @@
         <v>2.85</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.3</v>
@@ -2597,7 +2597,7 @@
         <v>4.2</v>
       </c>
       <c r="P14">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2633,7 +2633,7 @@
         <v>1.42</v>
       </c>
       <c r="AB14">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AC14">
         <v>2.17</v>
@@ -2766,7 +2766,7 @@
         <v>2.24</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
         <v>1.2</v>
@@ -2775,10 +2775,10 @@
         <v>3.9</v>
       </c>
       <c r="U15">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
         <v>1.14</v>
@@ -2796,7 +2796,7 @@
         <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC15">
         <v>2.04</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P18">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q18">
         <v>2.87</v>
@@ -3270,7 +3270,7 @@
         <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,13 +3282,13 @@
         <v>3.28</v>
       </c>
       <c r="AA18">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB18">
         <v>1.86</v>
       </c>
       <c r="AC18">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="AD18">
         <v>1.27</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
         <v>1.93</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P21">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q21">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="R21">
         <v>2.3</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1456,7 +1456,7 @@
         <v>3.7</v>
       </c>
       <c r="P7">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -1625,7 +1625,7 @@
         <v>1.65</v>
       </c>
       <c r="R8">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="S8">
         <v>1.14</v>
@@ -1634,10 +1634,10 @@
         <v>4.33</v>
       </c>
       <c r="U8">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="V8">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="W8">
         <v>1.17</v>
@@ -1652,7 +1652,7 @@
         <v>5.95</v>
       </c>
       <c r="AA8">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AB8">
         <v>2.7</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK8">
         <v>3.35</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1782,13 +1782,13 @@
         <v>3.45</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q9">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="S9">
         <v>1.34</v>
@@ -1809,22 +1809,22 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z9">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="AA9">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB9">
         <v>1.88</v>
       </c>
       <c r="AC9">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AD9">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE9">
         <v>1.12</v>
@@ -2932,28 +2932,28 @@
         <v>2.74</v>
       </c>
       <c r="S16">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="T16">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="V16">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W16">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Z16">
-        <v>6.73</v>
+        <v>7.25</v>
       </c>
       <c r="AA16">
         <v>1.4</v>
@@ -2968,13 +2968,13 @@
         <v>1.76</v>
       </c>
       <c r="AE16">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF16">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="O17">
         <v>6.3</v>
@@ -3089,25 +3089,25 @@
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
         <v>2.93</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="U17">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V17">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3119,10 +3119,10 @@
         <v>6.45</v>
       </c>
       <c r="AA17">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AB17">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
       <c r="AC17">
         <v>1.93</v>
@@ -3134,7 +3134,7 @@
         <v>1.33</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG17">
         <v>1.9</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="O15">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P15">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q15">
         <v>2.24</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W15">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2793,10 +2793,10 @@
         <v>5.51</v>
       </c>
       <c r="AA15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB15">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC15">
         <v>2.04</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>4.23</v>
+        <v>3.95</v>
       </c>
       <c r="Q20">
         <v>2.2</v>
@@ -3587,13 +3587,13 @@
         <v>1.35</v>
       </c>
       <c r="T20">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="U20">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3602,7 +3602,7 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
         <v>3.42</v>
@@ -3611,7 +3611,7 @@
         <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AC20">
         <v>3.29</v>
@@ -3642,7 +3642,7 @@
         <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         <v>2.15</v>
       </c>
       <c r="O21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
         <v>3</v>
       </c>
       <c r="Q21">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
         <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T21">
-        <v>3.6</v>
+        <v>3.26</v>
       </c>
       <c r="U21">
         <v>2.25</v>
@@ -3771,10 +3771,10 @@
         <v>4.36</v>
       </c>
       <c r="AA21">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
         <v>2.56</v>
@@ -3805,7 +3805,7 @@
         <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2274,7 +2274,7 @@
         <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="R12">
         <v>2.19</v>
@@ -2283,10 +2283,10 @@
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="V12">
         <v>1.47</v>
@@ -2295,25 +2295,25 @@
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.88</v>
+        <v>4.13</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC12">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE12">
         <v>1.11</v>
@@ -2322,7 +2322,7 @@
         <v>1.56</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>4.2</v>
       </c>
       <c r="P14">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2618,19 +2618,19 @@
         <v>1.67</v>
       </c>
       <c r="W14">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z14">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="AA14">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AB14">
         <v>2.6</v>
@@ -2639,13 +2639,13 @@
         <v>2.17</v>
       </c>
       <c r="AD14">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AE14">
         <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG14">
         <v>2.3</v>
@@ -3246,7 +3246,7 @@
         <v>2.37</v>
       </c>
       <c r="O18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.65</v>
@@ -3316,7 +3316,7 @@
         <v>1.38</v>
       </c>
       <c r="AK18">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,34 +3406,34 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O19">
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="V19">
         <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3448,13 +3448,13 @@
         <v>1.72</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AC19">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AD19">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
         <v>1.1</v>
@@ -4070,19 +4070,19 @@
         <v>2.88</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S23">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="U23">
         <v>2.62</v>
       </c>
       <c r="V23">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="W23">
         <v>1.06</v>
@@ -4103,19 +4103,19 @@
         <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF23">
         <v>1.7</v>
       </c>
       <c r="AG23">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="O24">
         <v>3.48</v>
@@ -4245,19 +4245,19 @@
         <v>2.62</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W24">
         <v>1.07</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
         <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
         <v>1.85</v>
@@ -4275,7 +4275,7 @@
         <v>1.12</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
         <v>2.05</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="AK24">
         <v>1.31</v>
@@ -4396,7 +4396,7 @@
         <v>3.02</v>
       </c>
       <c r="R25">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S25">
         <v>1.38</v>
@@ -4411,7 +4411,7 @@
         <v>1.35</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -4420,22 +4420,22 @@
         <v>1.36</v>
       </c>
       <c r="Z25">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AA25">
         <v>2.18</v>
       </c>
       <c r="AB25">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC25">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="AD25">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF25">
         <v>1.83</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -674,10 +674,10 @@
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -807,22 +807,22 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W3">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -852,10 +852,10 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -1456,43 +1456,43 @@
         <v>3.7</v>
       </c>
       <c r="P7">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q7">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="R7">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="U7">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X7">
         <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="AA7">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB7">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC7">
         <v>3.71</v>
@@ -1628,7 +1628,7 @@
         <v>2.73</v>
       </c>
       <c r="S8">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T8">
         <v>4.33</v>
@@ -1655,7 +1655,7 @@
         <v>1.36</v>
       </c>
       <c r="AB8">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC8">
         <v>1.99</v>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AK8">
         <v>3.35</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O9">
         <v>3.45</v>
       </c>
       <c r="P9">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="Q9">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="R9">
         <v>2.2</v>
@@ -1815,10 +1815,10 @@
         <v>3.38</v>
       </c>
       <c r="AA9">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AB9">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
         <v>3.04</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.85</v>
+        <v>2.64</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
         <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>3.34</v>
+        <v>2.94</v>
       </c>
       <c r="R12">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T12">
         <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W12">
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z12">
-        <v>4.13</v>
+        <v>3.67</v>
       </c>
       <c r="AA12">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AC12">
-        <v>2.72</v>
+        <v>3.03</v>
       </c>
       <c r="AD12">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF12">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
         <v>1.36</v>
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="O13">
         <v>4.2</v>
       </c>
       <c r="P13">
-        <v>6</v>
+        <v>7.26</v>
       </c>
       <c r="Q13">
         <v>1.95</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
         <v>3</v>
@@ -2467,10 +2467,10 @@
         <v>3.34</v>
       </c>
       <c r="AA13">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK13">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="O14">
         <v>4.2</v>
       </c>
       <c r="P14">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2618,7 +2618,7 @@
         <v>1.67</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X14">
         <v>1.02</v>
@@ -2630,22 +2630,22 @@
         <v>5.5</v>
       </c>
       <c r="AA14">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC14">
         <v>2.17</v>
       </c>
       <c r="AD14">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE14">
         <v>1.22</v>
       </c>
       <c r="AF14">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
         <v>2.3</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O15">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P15">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q15">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
         <v>1.2</v>
@@ -2775,10 +2775,10 @@
         <v>4</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V15">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
         <v>1.17</v>
@@ -2787,25 +2787,25 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5.51</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC15">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AD15">
         <v>1.67</v>
       </c>
       <c r="AE15">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AF15">
         <v>1.5</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AK15">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,25 +2926,25 @@
         <v>1.31</v>
       </c>
       <c r="Q16">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="S16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="U16">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V16">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W16">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2962,7 +2962,7 @@
         <v>2.83</v>
       </c>
       <c r="AC16">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AD16">
         <v>1.76</v>
@@ -2971,10 +2971,10 @@
         <v>1.29</v>
       </c>
       <c r="AF16">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK16">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="O17">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="P17">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="Q17">
         <v>1.52</v>
@@ -3101,10 +3101,10 @@
         <v>4.6</v>
       </c>
       <c r="U17">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="V17">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="W17">
         <v>1.19</v>
@@ -3113,10 +3113,10 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>6.45</v>
+        <v>6.55</v>
       </c>
       <c r="AA17">
         <v>1.32</v>
@@ -3125,19 +3125,19 @@
         <v>2.95</v>
       </c>
       <c r="AC17">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AD17">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AE17">
         <v>1.33</v>
       </c>
       <c r="AF17">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG17">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O18">
         <v>3.3</v>
       </c>
       <c r="P18">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="Q18">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
         <v>2.06</v>
@@ -3273,7 +3273,7 @@
         <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
         <v>1.25</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
         <v>1.44</v>
@@ -3406,58 +3406,58 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
-        <v>4.2</v>
+        <v>3.61</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S19">
         <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="U19">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
         <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AA19">
         <v>1.72</v>
       </c>
       <c r="AB19">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AC19">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF19">
         <v>1.62</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,31 +3569,31 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
-        <v>3.95</v>
+        <v>4.23</v>
       </c>
       <c r="Q20">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R20">
         <v>2.2</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="U20">
         <v>2.88</v>
       </c>
       <c r="V20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z20">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB20">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC20">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="AD20">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE20">
         <v>1.08</v>
       </c>
       <c r="AF20">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.25</v>
       </c>
       <c r="AK20">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
         <v>3</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R21">
         <v>2.3</v>
@@ -3753,10 +3753,10 @@
         <v>3.26</v>
       </c>
       <c r="U21">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="V21">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W21">
         <v>1.11</v>
@@ -3765,7 +3765,7 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
         <v>4.36</v>
@@ -3783,13 +3783,13 @@
         <v>1.52</v>
       </c>
       <c r="AE21">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
         <v>1.47</v>
       </c>
       <c r="AG21">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AK21">
         <v>1.62</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.53</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="Q23">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="R23">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="S23">
+        <v>1.33</v>
+      </c>
+      <c r="T23">
+        <v>2.96</v>
+      </c>
+      <c r="U23">
+        <v>2.58</v>
+      </c>
+      <c r="V23">
+        <v>1.44</v>
+      </c>
+      <c r="W23">
+        <v>1.07</v>
+      </c>
+      <c r="X23">
+        <v>1.02</v>
+      </c>
+      <c r="Y23">
+        <v>1.26</v>
+      </c>
+      <c r="Z23">
+        <v>3.61</v>
+      </c>
+      <c r="AA23">
+        <v>1.74</v>
+      </c>
+      <c r="AB23">
+        <v>2.08</v>
+      </c>
+      <c r="AC23">
+        <v>2.9</v>
+      </c>
+      <c r="AD23">
         <v>1.36</v>
       </c>
-      <c r="T23">
-        <v>2.81</v>
-      </c>
-      <c r="U23">
-        <v>2.62</v>
-      </c>
-      <c r="V23">
-        <v>1.38</v>
-      </c>
-      <c r="W23">
-        <v>1.06</v>
-      </c>
-      <c r="X23">
-        <v>1.03</v>
-      </c>
-      <c r="Y23">
-        <v>1.31</v>
-      </c>
-      <c r="Z23">
-        <v>3.24</v>
-      </c>
-      <c r="AA23">
-        <v>1.95</v>
-      </c>
-      <c r="AB23">
-        <v>1.85</v>
-      </c>
-      <c r="AC23">
-        <v>3.4</v>
-      </c>
-      <c r="AD23">
-        <v>1.29</v>
-      </c>
       <c r="AE23">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF23">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O24">
         <v>3.48</v>
       </c>
       <c r="P24">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="Q24">
+        <v>4.1</v>
+      </c>
+      <c r="R24">
+        <v>2.3</v>
+      </c>
+      <c r="S24">
+        <v>1.32</v>
+      </c>
+      <c r="T24">
+        <v>3.28</v>
+      </c>
+      <c r="U24">
+        <v>2.58</v>
+      </c>
+      <c r="V24">
+        <v>1.45</v>
+      </c>
+      <c r="W24">
+        <v>1.08</v>
+      </c>
+      <c r="X24">
+        <v>1.02</v>
+      </c>
+      <c r="Y24">
+        <v>1.25</v>
+      </c>
+      <c r="Z24">
         <v>4</v>
       </c>
-      <c r="R24">
-        <v>2.14</v>
-      </c>
-      <c r="S24">
-        <v>1.33</v>
-      </c>
-      <c r="T24">
-        <v>2.97</v>
-      </c>
-      <c r="U24">
-        <v>2.62</v>
-      </c>
-      <c r="V24">
-        <v>1.46</v>
-      </c>
-      <c r="W24">
-        <v>1.07</v>
-      </c>
-      <c r="X24">
-        <v>1.03</v>
-      </c>
-      <c r="Y24">
-        <v>1.27</v>
-      </c>
-      <c r="Z24">
-        <v>3.6</v>
-      </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AD24">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE24">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF24">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AK24">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O25">
+        <v>3.36</v>
+      </c>
+      <c r="P25">
+        <v>2.35</v>
+      </c>
+      <c r="Q25">
         <v>3.3</v>
       </c>
-      <c r="P25">
-        <v>3</v>
-      </c>
-      <c r="Q25">
-        <v>3.02</v>
-      </c>
       <c r="R25">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="U25">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="V25">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC25">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD25">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF25">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AG25">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK25">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="O9">
         <v>3.45</v>
@@ -1785,7 +1785,7 @@
         <v>3.28</v>
       </c>
       <c r="Q9">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
         <v>2.2</v>
@@ -1815,10 +1815,10 @@
         <v>3.38</v>
       </c>
       <c r="AA9">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB9">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC9">
         <v>3.04</v>
@@ -2268,10 +2268,10 @@
         <v>2.64</v>
       </c>
       <c r="O12">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q12">
         <v>2.94</v>
@@ -2286,7 +2286,7 @@
         <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="V12">
         <v>1.45</v>
@@ -2298,22 +2298,22 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="AA12">
         <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC12">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
         <v>1.09</v>
@@ -2338,7 +2338,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>4.2</v>
       </c>
       <c r="P14">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2763,7 +2763,7 @@
         <v>4.4</v>
       </c>
       <c r="Q15">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R15">
         <v>2.5</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="O16">
         <v>5.4</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="O17">
         <v>7.7</v>
@@ -3134,7 +3134,7 @@
         <v>1.33</v>
       </c>
       <c r="AF17">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
         <v>1.92</v>
@@ -3249,10 +3249,10 @@
         <v>3.3</v>
       </c>
       <c r="P18">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R18">
         <v>2.06</v>
@@ -3273,7 +3273,7 @@
         <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
         <v>1.25</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="O19">
         <v>3.3</v>
@@ -3436,7 +3436,7 @@
         <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.18</v>
@@ -3445,7 +3445,7 @@
         <v>3.88</v>
       </c>
       <c r="AA19">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB19">
         <v>2.07</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3771,7 +3771,7 @@
         <v>4.36</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB21">
         <v>2.33</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
         <v>1.62</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="O23">
         <v>3.53</v>
@@ -4097,7 +4097,7 @@
         <v>3.61</v>
       </c>
       <c r="AA23">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
         <v>2.08</v>
@@ -4221,16 +4221,16 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O24">
-        <v>3.48</v>
+        <v>3.72</v>
       </c>
       <c r="P24">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q24">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="R24">
         <v>2.3</v>
@@ -4254,10 +4254,10 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="AA24">
         <v>1.75</v>
@@ -4266,16 +4266,16 @@
         <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AD24">
         <v>1.42</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG24">
         <v>2.15</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AK24">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="O25">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="Q25">
         <v>3.3</v>
@@ -4402,13 +4402,13 @@
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U25">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="V25">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W25">
         <v>1.06</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1456,7 +1456,7 @@
         <v>3.7</v>
       </c>
       <c r="P7">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Q7">
         <v>6.5</v>
@@ -1468,7 +1468,7 @@
         <v>1.36</v>
       </c>
       <c r="T7">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
         <v>2.99</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
         <v>3.28</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="O13">
         <v>4.2</v>
@@ -2470,7 +2470,7 @@
         <v>1.87</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC13">
         <v>3.2</v>
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
       <c r="P15">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q15">
         <v>2.24</v>
@@ -2802,7 +2802,7 @@
         <v>2.14</v>
       </c>
       <c r="AD15">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE15">
         <v>1.29</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>8.4</v>
+        <v>1.25</v>
       </c>
       <c r="O16">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>6</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="S16">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V16">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>7.25</v>
+        <v>6.55</v>
       </c>
       <c r="AA16">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AB16">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AC16">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="AD16">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AE16">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK16">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.15</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>7.7</v>
+        <v>5.4</v>
       </c>
       <c r="P17">
-        <v>13.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>6.5</v>
       </c>
       <c r="R17">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="S17">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T17">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W17">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z17">
-        <v>6.55</v>
+        <v>7.25</v>
       </c>
       <c r="AA17">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AC17">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="AD17">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AE17">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>4.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="O21">
         <v>3.8</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="Q21">
         <v>2.6</v>
@@ -3747,7 +3747,7 @@
         <v>2.3</v>
       </c>
       <c r="S21">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
         <v>3.26</v>
@@ -3771,10 +3771,10 @@
         <v>4.36</v>
       </c>
       <c r="AA21">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AC21">
         <v>2.56</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O12">
         <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
         <v>2.94</v>
@@ -2304,7 +2304,7 @@
         <v>3.69</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
         <v>1.92</v>
@@ -2594,10 +2594,10 @@
         <v>1.4</v>
       </c>
       <c r="O14">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P14">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -3243,28 +3243,28 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R18">
         <v>2.06</v>
       </c>
       <c r="S18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U18">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V18">
         <v>1.4</v>
@@ -3285,7 +3285,7 @@
         <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC18">
         <v>3.27</v>
@@ -3316,7 +3316,7 @@
         <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,10 +3409,10 @@
         <v>2.77</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q19">
         <v>3.61</v>
@@ -3433,7 +3433,7 @@
         <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3445,13 +3445,13 @@
         <v>3.88</v>
       </c>
       <c r="AA19">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB19">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="AC19">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AD19">
         <v>1.36</v>
@@ -3578,10 +3578,10 @@
         <v>4.23</v>
       </c>
       <c r="Q20">
+        <v>2.25</v>
+      </c>
+      <c r="R20">
         <v>2.15</v>
-      </c>
-      <c r="R20">
-        <v>2.2</v>
       </c>
       <c r="S20">
         <v>1.36</v>
@@ -3608,10 +3608,10 @@
         <v>3.44</v>
       </c>
       <c r="AA20">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC20">
         <v>3.26</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="O23">
         <v>3.53</v>
       </c>
       <c r="P23">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="Q23">
         <v>2.76</v>
@@ -4073,7 +4073,7 @@
         <v>2.13</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
         <v>2.96</v>
@@ -4224,13 +4224,13 @@
         <v>3.75</v>
       </c>
       <c r="O24">
-        <v>3.72</v>
+        <v>3.33</v>
       </c>
       <c r="P24">
         <v>1.85</v>
       </c>
       <c r="Q24">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="R24">
         <v>2.3</v>
@@ -4242,37 +4242,37 @@
         <v>3.28</v>
       </c>
       <c r="U24">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="V24">
         <v>1.45</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AA24">
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="AC24">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="AD24">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
         <v>1.63</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AK24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P25">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="Q25">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R25">
         <v>2.25</v>
@@ -4402,7 +4402,7 @@
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U25">
         <v>2.62</v>
@@ -4411,7 +4411,7 @@
         <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -4420,25 +4420,25 @@
         <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA25">
         <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC25">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD25">
         <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
         <v>2.1</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="O2">
-        <v>4.45</v>
+        <v>3.92</v>
       </c>
       <c r="P2">
-        <v>8.9</v>
+        <v>6.7</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -1779,13 +1779,13 @@
         <v>2.1</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
         <v>3.28</v>
       </c>
       <c r="Q9">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R9">
         <v>2.2</v>
@@ -1833,7 +1833,7 @@
         <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="O11">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="O12">
         <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q12">
         <v>2.94</v>
@@ -2286,7 +2286,7 @@
         <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="V12">
         <v>1.45</v>
@@ -2301,16 +2301,16 @@
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="AA12">
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AC12">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="AD12">
         <v>1.36</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P14">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2926,10 +2926,10 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R16">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="S16">
         <v>1.13</v>
@@ -2950,7 +2950,7 @@
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z16">
         <v>6.55</v>
@@ -2974,7 +2974,7 @@
         <v>1.75</v>
       </c>
       <c r="AG16">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.7</v>
@@ -3285,7 +3285,7 @@
         <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC18">
         <v>3.27</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q19">
         <v>3.61</v>
@@ -3750,7 +3750,7 @@
         <v>1.3</v>
       </c>
       <c r="T21">
-        <v>3.26</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
         <v>2.45</v>
@@ -3771,10 +3771,10 @@
         <v>4.36</v>
       </c>
       <c r="AA21">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AB21">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
         <v>2.56</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="O23">
-        <v>3.53</v>
+        <v>3.48</v>
       </c>
       <c r="P23">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="Q23">
         <v>2.76</v>
@@ -4097,10 +4097,10 @@
         <v>3.61</v>
       </c>
       <c r="AA23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB23">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
         <v>2.9</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="O24">
-        <v>3.33</v>
+        <v>3.58</v>
       </c>
       <c r="P24">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Q24">
         <v>4.3</v>
@@ -4260,7 +4260,7 @@
         <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
         <v>2.13</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="Q25">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S25">
         <v>1.35</v>
@@ -4411,7 +4411,7 @@
         <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O9">
         <v>3.45</v>
@@ -1794,7 +1794,7 @@
         <v>1.34</v>
       </c>
       <c r="T9">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="U9">
         <v>2.64</v>
@@ -1818,7 +1818,7 @@
         <v>1.88</v>
       </c>
       <c r="AB9">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC9">
         <v>3.04</v>
@@ -1833,7 +1833,7 @@
         <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2295,19 +2295,19 @@
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z12">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA12">
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>3</v>
@@ -2316,10 +2316,10 @@
         <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
         <v>2.2</v>
@@ -2594,10 +2594,10 @@
         <v>1.48</v>
       </c>
       <c r="O14">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="P14">
-        <v>5.25</v>
+        <v>5.66</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2621,13 +2621,13 @@
         <v>1.18</v>
       </c>
       <c r="X14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <v>1.5</v>
@@ -2636,19 +2636,19 @@
         <v>2.5</v>
       </c>
       <c r="AC14">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AD14">
         <v>1.62</v>
       </c>
       <c r="AE14">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF14">
         <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
       <c r="P15">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
         <v>2.24</v>
@@ -2926,10 +2926,10 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R16">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="S16">
         <v>1.13</v>
@@ -2944,16 +2944,16 @@
         <v>1.78</v>
       </c>
       <c r="W16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA16">
         <v>1.32</v>
@@ -2962,13 +2962,13 @@
         <v>2.95</v>
       </c>
       <c r="AC16">
+        <v>1.9</v>
+      </c>
+      <c r="AD16">
         <v>1.87</v>
       </c>
-      <c r="AD16">
-        <v>1.8</v>
-      </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF16">
         <v>1.75</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O17">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="P17">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q17">
         <v>6.5</v>
@@ -3113,31 +3113,31 @@
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z17">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA17">
         <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AC17">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AD17">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AE17">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
@@ -3273,13 +3273,13 @@
         <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z18">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA18">
         <v>1.96</v>
@@ -3288,16 +3288,16 @@
         <v>1.86</v>
       </c>
       <c r="AC18">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="AD18">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
         <v>2.05</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P19">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q19">
         <v>3.61</v>
@@ -3439,10 +3439,10 @@
         <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA19">
         <v>1.75</v>
@@ -3454,16 +3454,16 @@
         <v>2.84</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF19">
         <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>2.33</v>
       </c>
       <c r="O23">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
         <v>2.7</v>
@@ -4426,7 +4426,7 @@
         <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>3.25</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -644,34 +644,34 @@
         <v>6.7</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA2">
         <v>1.9</v>
@@ -680,19 +680,19 @@
         <v>1.9</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q8">
         <v>1.65</v>
@@ -1646,10 +1646,10 @@
         <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z8">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="AA8">
         <v>1.36</v>
@@ -1658,19 +1658,19 @@
         <v>2.88</v>
       </c>
       <c r="AC8">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AD8">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE8">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AF8">
         <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
         <v>3.45</v>
@@ -1833,7 +1833,7 @@
         <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2111,34 +2111,34 @@
         <v>3.5</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA11">
         <v>2.2</v>
@@ -2147,19 +2147,19 @@
         <v>1.65</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2271,7 +2271,7 @@
         <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q12">
         <v>2.94</v>
@@ -2458,34 +2458,34 @@
         <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
         <v>1.87</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD13">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
         <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="O14">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="P14">
-        <v>5.66</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
       <c r="P15">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="Q15">
         <v>2.24</v>
@@ -2769,10 +2769,10 @@
         <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U15">
         <v>2.26</v>
@@ -2787,25 +2787,25 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB15">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC15">
         <v>2.14</v>
       </c>
       <c r="AD15">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AE15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
         <v>1.5</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="O16">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -2929,7 +2929,7 @@
         <v>1.52</v>
       </c>
       <c r="R16">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="S16">
         <v>1.13</v>
@@ -3083,10 +3083,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="P17">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="Q17">
         <v>6.5</v>
@@ -3246,10 +3246,10 @@
         <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="P18">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Q18">
         <v>2.88</v>
@@ -3285,7 +3285,7 @@
         <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC18">
         <v>3.4</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="O19">
         <v>3.55</v>
       </c>
       <c r="P19">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="Q19">
         <v>3.61</v>
@@ -3741,7 +3741,7 @@
         <v>2.67</v>
       </c>
       <c r="Q21">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="R21">
         <v>2.3</v>
@@ -4064,7 +4064,7 @@
         <v>3.5</v>
       </c>
       <c r="P23">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q23">
         <v>2.76</v>
@@ -4091,16 +4091,16 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="AA23">
         <v>1.74</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AC23">
         <v>2.9</v>
@@ -4109,7 +4109,7 @@
         <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
         <v>1.57</v>
@@ -4131,7 +4131,7 @@
         <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
         <v>4.3</v>
@@ -4254,13 +4254,13 @@
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
         <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB24">
         <v>2.13</v>
@@ -4269,13 +4269,13 @@
         <v>2.79</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE24">
         <v>1.12</v>
       </c>
       <c r="AF24">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG24">
         <v>2.15</v>
@@ -4390,7 +4390,7 @@
         <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="Q25">
         <v>3.05</v>
@@ -4426,7 +4426,7 @@
         <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC25">
         <v>3.25</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -674,7 +674,7 @@
         <v>3.48</v>
       </c>
       <c r="AA2">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AB2">
         <v>1.9</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O9">
         <v>3.45</v>
@@ -1785,7 +1785,7 @@
         <v>3.28</v>
       </c>
       <c r="Q9">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R9">
         <v>2.2</v>
@@ -1830,10 +1830,10 @@
         <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
         <v>1.67</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
         <v>4.4</v>
       </c>
       <c r="P14">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.22</v>
+        <v>7.75</v>
       </c>
       <c r="O16">
+        <v>6.13</v>
+      </c>
+      <c r="P16">
+        <v>1.32</v>
+      </c>
+      <c r="Q16">
         <v>6.5</v>
       </c>
-      <c r="P16">
-        <v>10</v>
-      </c>
-      <c r="Q16">
-        <v>1.52</v>
-      </c>
       <c r="R16">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="S16">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="T16">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V16">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W16">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2956,25 +2956,25 @@
         <v>6.5</v>
       </c>
       <c r="AA16">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AC16">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD16">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AE16">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK16">
-        <v>4.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>9.199999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="O17">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="P17">
-        <v>1.21</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>6.5</v>
+        <v>1.52</v>
       </c>
       <c r="R17">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="S17">
+        <v>1.13</v>
+      </c>
+      <c r="T17">
+        <v>4.6</v>
+      </c>
+      <c r="U17">
+        <v>1.98</v>
+      </c>
+      <c r="V17">
+        <v>1.78</v>
+      </c>
+      <c r="W17">
         <v>1.2</v>
-      </c>
-      <c r="T17">
-        <v>4</v>
-      </c>
-      <c r="U17">
-        <v>2</v>
-      </c>
-      <c r="V17">
-        <v>1.71</v>
-      </c>
-      <c r="W17">
-        <v>1.17</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3119,25 +3119,25 @@
         <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AB17">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AC17">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AD17">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AE17">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK17">
-        <v>1.07</v>
+        <v>4.5</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.7</v>
@@ -3409,7 +3409,7 @@
         <v>2.75</v>
       </c>
       <c r="O19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P19">
         <v>2.31</v>
@@ -3448,7 +3448,7 @@
         <v>1.75</v>
       </c>
       <c r="AB19">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AC19">
         <v>2.84</v>
@@ -4079,7 +4079,7 @@
         <v>2.96</v>
       </c>
       <c r="U23">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="O24">
         <v>3.9</v>
@@ -4260,7 +4260,7 @@
         <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB24">
         <v>2.13</v>
@@ -4426,7 +4426,7 @@
         <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC25">
         <v>3.25</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -686,7 +686,7 @@
         <v>1.33</v>
       </c>
       <c r="AE2">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF2">
         <v>1.91</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="O9">
         <v>3.45</v>
@@ -1797,7 +1797,7 @@
         <v>2.9</v>
       </c>
       <c r="U9">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="V9">
         <v>1.38</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="P10">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="N16">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="O16">
-        <v>6.13</v>
+        <v>5.5</v>
       </c>
       <c r="P16">
         <v>1.32</v>
@@ -2959,7 +2959,7 @@
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="AC16">
         <v>2.1</v>
@@ -3092,19 +3092,19 @@
         <v>1.52</v>
       </c>
       <c r="R17">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="S17">
         <v>1.13</v>
       </c>
       <c r="T17">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="U17">
         <v>1.98</v>
       </c>
       <c r="V17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="W17">
         <v>1.2</v>
@@ -3119,10 +3119,10 @@
         <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB17">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AC17">
         <v>1.9</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1948,34 +1948,34 @@
         <v>2.33</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA10">
         <v>2.1</v>
@@ -1984,19 +1984,19 @@
         <v>1.7</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="V12">
         <v>1.45</v>
@@ -2304,13 +2304,13 @@
         <v>4.1</v>
       </c>
       <c r="AA12">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AD12">
         <v>1.36</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="P14">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>1.99</v>
@@ -2627,22 +2627,22 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>5.49</v>
       </c>
       <c r="AA14">
         <v>1.5</v>
       </c>
       <c r="AB14">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC14">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AD14">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE14">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF14">
         <v>1.57</v>
@@ -2793,7 +2793,7 @@
         <v>6.5</v>
       </c>
       <c r="AA15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB15">
         <v>2.88</v>
@@ -3246,7 +3246,7 @@
         <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="P18">
         <v>2.7</v>
@@ -3412,7 +3412,7 @@
         <v>3.5</v>
       </c>
       <c r="P19">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="Q19">
         <v>3.61</v>
@@ -3445,13 +3445,13 @@
         <v>4.1</v>
       </c>
       <c r="AA19">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB19">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC19">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AD19">
         <v>1.4</v>
@@ -3771,7 +3771,7 @@
         <v>4.36</v>
       </c>
       <c r="AA21">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB21">
         <v>2.33</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P23">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="Q23">
         <v>2.76</v>
@@ -4076,13 +4076,13 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>2.96</v>
+        <v>3.21</v>
       </c>
       <c r="U23">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4103,7 +4103,7 @@
         <v>2.08</v>
       </c>
       <c r="AC23">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AD23">
         <v>1.36</v>
@@ -4112,7 +4112,7 @@
         <v>1.13</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG23">
         <v>2.25</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q24">
         <v>4.3</v>
@@ -4236,7 +4236,7 @@
         <v>2.3</v>
       </c>
       <c r="S24">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
         <v>3.28</v>
@@ -4260,7 +4260,7 @@
         <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB24">
         <v>2.13</v>
@@ -4390,7 +4390,7 @@
         <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="Q25">
         <v>3.05</v>
@@ -4426,7 +4426,7 @@
         <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC25">
         <v>3.25</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
         <v>1.5</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1320,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA6">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>3.7</v>
       </c>
       <c r="P7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q7">
         <v>6.5</v>
@@ -1465,19 +1465,19 @@
         <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
         <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.01</v>
@@ -1495,7 +1495,7 @@
         <v>1.68</v>
       </c>
       <c r="AC7">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="AD7">
         <v>1.26</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
         <v>3.28</v>
@@ -1788,7 +1788,7 @@
         <v>2.7</v>
       </c>
       <c r="R9">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S9">
         <v>1.34</v>
@@ -1849,7 +1849,7 @@
         <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1981,7 +1981,7 @@
         <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
         <v>4.1</v>
@@ -2141,10 +2141,10 @@
         <v>2.74</v>
       </c>
       <c r="AA11">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB11">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
         <v>3.8</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="O12">
         <v>3.3</v>
@@ -2274,10 +2274,10 @@
         <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="R12">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
         <v>1.34</v>
@@ -2289,7 +2289,7 @@
         <v>2.73</v>
       </c>
       <c r="V12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
         <v>1.1</v>
@@ -2304,7 +2304,7 @@
         <v>4.1</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB12">
         <v>1.93</v>
@@ -2431,7 +2431,7 @@
         <v>1.4</v>
       </c>
       <c r="O13">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P13">
         <v>7.26</v>
@@ -2443,7 +2443,7 @@
         <v>2.38</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
         <v>3</v>
@@ -2455,19 +2455,19 @@
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB13">
         <v>1.9</v>
@@ -2482,10 +2482,10 @@
         <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK13">
         <v>2.58</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O14">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="P14">
         <v>5</v>
@@ -2603,13 +2603,13 @@
         <v>1.99</v>
       </c>
       <c r="R14">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="S14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T14">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U14">
         <v>2.1</v>
@@ -2627,13 +2627,13 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5.49</v>
+        <v>5.51</v>
       </c>
       <c r="AA14">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB14">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AC14">
         <v>2.21</v>
@@ -2642,7 +2642,7 @@
         <v>1.67</v>
       </c>
       <c r="AE14">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF14">
         <v>1.57</v>
@@ -2664,7 +2664,7 @@
         <v>1.15</v>
       </c>
       <c r="AK14">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,34 +2754,34 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P15">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
         <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
         <v>4.5</v>
       </c>
       <c r="U15">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="V15">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2796,7 +2796,7 @@
         <v>1.44</v>
       </c>
       <c r="AB15">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC15">
         <v>2.14</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK15">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>7.5</v>
       </c>
       <c r="O16">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="P16">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Q16">
         <v>6.5</v>
@@ -2959,7 +2959,7 @@
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AC16">
         <v>2.1</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK16">
         <v>1.07</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="O17">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="P17">
         <v>10</v>
@@ -3122,13 +3122,13 @@
         <v>1.36</v>
       </c>
       <c r="AB17">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AC17">
         <v>1.9</v>
       </c>
       <c r="AD17">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE17">
         <v>1.36</v>
@@ -3246,19 +3246,19 @@
         <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="Q18">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R18">
         <v>2.06</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
         <v>2.88</v>
@@ -3270,7 +3270,7 @@
         <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
         <v>1.04</v>
@@ -3285,7 +3285,7 @@
         <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC18">
         <v>3.4</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O19">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="P19">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q19">
         <v>3.61</v>
@@ -3421,10 +3421,10 @@
         <v>2.18</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T19">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="U19">
         <v>2.5</v>
@@ -3442,22 +3442,22 @@
         <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA19">
         <v>1.76</v>
       </c>
       <c r="AB19">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC19">
         <v>2.86</v>
       </c>
       <c r="AD19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
         <v>1.62</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AK19">
         <v>1.36</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>4.23</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
         <v>2.25</v>
@@ -3587,7 +3587,7 @@
         <v>1.36</v>
       </c>
       <c r="T20">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="U20">
         <v>2.88</v>
@@ -3602,22 +3602,22 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z20">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="AA20">
         <v>1.9</v>
       </c>
       <c r="AB20">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AC20">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="AD20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE20">
         <v>1.08</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="O21">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P21">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="Q21">
         <v>2.63</v>
@@ -3768,13 +3768,13 @@
         <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="AA21">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AC21">
         <v>2.56</v>
@@ -3910,19 +3910,19 @@
         <v>1.85</v>
       </c>
       <c r="S22">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T22">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="U22">
         <v>3.6</v>
       </c>
       <c r="V22">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22">
         <v>1.08</v>
@@ -4061,13 +4061,13 @@
         <v>2.28</v>
       </c>
       <c r="O23">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="P23">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="Q23">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="R23">
         <v>2.13</v>
@@ -4076,13 +4076,13 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="U23">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4103,7 +4103,7 @@
         <v>2.08</v>
       </c>
       <c r="AC23">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="AD23">
         <v>1.36</v>
@@ -4115,7 +4115,7 @@
         <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
         <v>4.3</v>
@@ -4242,7 +4242,7 @@
         <v>3.28</v>
       </c>
       <c r="U24">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
         <v>1.45</v>
@@ -4263,16 +4263,16 @@
         <v>1.72</v>
       </c>
       <c r="AB24">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="AC24">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AD24">
         <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
         <v>1.65</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q25">
         <v>3.05</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -644,16 +644,16 @@
         <v>6.7</v>
       </c>
       <c r="Q2">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="R2">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U2">
         <v>2.45</v>
@@ -662,7 +662,7 @@
         <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.02</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="O4">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="P4">
-        <v>5.65</v>
+        <v>4.4</v>
       </c>
       <c r="Q4">
-        <v>2.57</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="S4">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="T4">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="U4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Y4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Z4">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AA4">
         <v>2.7</v>
       </c>
       <c r="AB4">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AC4">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="AD4">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AE4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="AG4">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
         <v>1.95</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.47</v>
+        <v>1.48</v>
       </c>
       <c r="O5">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>4.35</v>
+        <v>2.09</v>
       </c>
       <c r="R5">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S5">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T5">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="U5">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
         <v>1.01</v>
       </c>
       <c r="X5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y5">
         <v>1.5</v>
       </c>
       <c r="Z5">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="AA5">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AB5">
         <v>1.41</v>
       </c>
       <c r="AC5">
-        <v>5.05</v>
+        <v>5.3</v>
       </c>
       <c r="AD5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF5">
-        <v>2.11</v>
+        <v>2.83</v>
       </c>
       <c r="AG5">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="O6">
-        <v>3.52</v>
+        <v>2.87</v>
       </c>
       <c r="P6">
-        <v>7.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="Z6">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="O9">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="P9">
         <v>3.28</v>
@@ -1791,7 +1791,7 @@
         <v>2.08</v>
       </c>
       <c r="S9">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="T9">
         <v>2.9</v>
@@ -1806,7 +1806,7 @@
         <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
         <v>1.24</v>
@@ -1821,10 +1821,10 @@
         <v>1.9</v>
       </c>
       <c r="AC9">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD9">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE9">
         <v>1.12</v>
@@ -2117,10 +2117,10 @@
         <v>1.95</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
-        <v>2.62</v>
+        <v>2.51</v>
       </c>
       <c r="U11">
         <v>3</v>
@@ -2129,7 +2129,7 @@
         <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2141,7 +2141,7 @@
         <v>2.74</v>
       </c>
       <c r="AA11">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB11">
         <v>1.6</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O14">
         <v>4.45</v>
@@ -2603,7 +2603,7 @@
         <v>1.99</v>
       </c>
       <c r="R14">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="S14">
         <v>1.2</v>
@@ -2627,16 +2627,16 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>5.51</v>
+        <v>5.48</v>
       </c>
       <c r="AA14">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB14">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AC14">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AD14">
         <v>1.67</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AK14">
         <v>2.6</v>
@@ -2763,10 +2763,10 @@
         <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S15">
         <v>1.22</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="O17">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="P17">
         <v>10</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R17">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="S17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U17">
         <v>1.98</v>
@@ -3246,16 +3246,16 @@
         <v>2.3</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P18">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
         <v>2.8</v>
       </c>
       <c r="R18">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
         <v>1.4</v>
@@ -3412,7 +3412,7 @@
         <v>3.52</v>
       </c>
       <c r="P19">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="Q19">
         <v>3.61</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O21">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="P21">
-        <v>3.06</v>
+        <v>2.67</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="R21">
         <v>2.3</v>
@@ -3765,16 +3765,16 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA21">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AC21">
         <v>2.56</v>
@@ -3805,7 +3805,7 @@
         <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O23">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="P23">
         <v>2.62</v>
@@ -4097,7 +4097,7 @@
         <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
         <v>2.08</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="P24">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q24">
         <v>4.3</v>
@@ -4251,7 +4251,7 @@
         <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y24">
         <v>1.2</v>
@@ -4263,16 +4263,16 @@
         <v>1.72</v>
       </c>
       <c r="AB24">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AD24">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF24">
         <v>1.65</v>
@@ -4402,7 +4402,7 @@
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="U25">
         <v>2.62</v>
@@ -4417,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z25">
         <v>3.6</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -635,25 +635,25 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="O2">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="P2">
-        <v>6.7</v>
+        <v>5.25</v>
       </c>
       <c r="Q2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U2">
         <v>2.45</v>
@@ -662,37 +662,37 @@
         <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="AA2">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB2">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC2">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE2">
         <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.16</v>
       </c>
       <c r="AK2">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="O7">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="P7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q7">
         <v>6.5</v>
@@ -1471,10 +1471,10 @@
         <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="V7">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W7">
         <v>1.07</v>
@@ -1495,7 +1495,7 @@
         <v>1.68</v>
       </c>
       <c r="AC7">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="AD7">
         <v>1.26</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="AK7">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="O10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="Q10">
-        <v>3.68</v>
+        <v>2.99</v>
       </c>
       <c r="R10">
         <v>2</v>
       </c>
       <c r="S10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="U10">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="V10">
         <v>1.35</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z10">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA10">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AB10">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AC10">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="AK10">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2117,7 +2117,7 @@
         <v>1.95</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T11">
         <v>2.51</v>
@@ -2129,7 +2129,7 @@
         <v>1.33</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK11">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2280,13 +2280,13 @@
         <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
         <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="V12">
         <v>1.46</v>
@@ -2307,19 +2307,19 @@
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC12">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE12">
         <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG12">
         <v>2.2</v>
@@ -2431,7 +2431,7 @@
         <v>1.4</v>
       </c>
       <c r="O13">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
         <v>7.26</v>
@@ -2440,7 +2440,7 @@
         <v>1.95</v>
       </c>
       <c r="R13">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2455,10 +2455,10 @@
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.25</v>
@@ -2470,16 +2470,16 @@
         <v>1.85</v>
       </c>
       <c r="AB13">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AC13">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF13">
         <v>2.1</v>
@@ -2544,27 +2544,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.48</v>
+        <v>2.37</v>
       </c>
       <c r="O14">
-        <v>4.45</v>
+        <v>2.7</v>
       </c>
       <c r="P14">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="Q14">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="S14">
+        <v>1.57</v>
+      </c>
+      <c r="T14">
+        <v>2.22</v>
+      </c>
+      <c r="U14">
+        <v>3.6</v>
+      </c>
+      <c r="V14">
         <v>1.2</v>
       </c>
-      <c r="T14">
-        <v>4</v>
-      </c>
-      <c r="U14">
-        <v>2.1</v>
-      </c>
-      <c r="V14">
-        <v>1.67</v>
-      </c>
       <c r="W14">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
+        <v>1.08</v>
+      </c>
+      <c r="Y14">
+        <v>1.53</v>
+      </c>
+      <c r="Z14">
+        <v>2.28</v>
+      </c>
+      <c r="AA14">
+        <v>2.62</v>
+      </c>
+      <c r="AB14">
+        <v>1.38</v>
+      </c>
+      <c r="AC14">
+        <v>5.75</v>
+      </c>
+      <c r="AD14">
+        <v>1.1</v>
+      </c>
+      <c r="AE14">
         <v>1.01</v>
       </c>
-      <c r="Y14">
-        <v>1.13</v>
-      </c>
-      <c r="Z14">
-        <v>5.48</v>
-      </c>
-      <c r="AA14">
-        <v>1.48</v>
-      </c>
-      <c r="AB14">
-        <v>2.62</v>
-      </c>
-      <c r="AC14">
-        <v>2.22</v>
-      </c>
-      <c r="AD14">
-        <v>1.67</v>
-      </c>
-      <c r="AE14">
-        <v>1.22</v>
-      </c>
       <c r="AF14">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="AG14">
-        <v>2.38</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.16</v>
+        <v>1.39</v>
       </c>
       <c r="AK14">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-10-29 14:30:00</t>
+          <t>2026-10-29 14:00:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,31 +2754,31 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="O15">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="P15">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="R15">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W15">
         <v>1.18</v>
@@ -2787,31 +2787,31 @@
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>6.5</v>
+        <v>5.55</v>
       </c>
       <c r="AA15">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB15">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AC15">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AD15">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AE15">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>7.5</v>
+        <v>1.65</v>
       </c>
       <c r="O16">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="P16">
-        <v>1.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>6.5</v>
+        <v>2.19</v>
       </c>
       <c r="R16">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="S16">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T16">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V16">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2956,25 +2956,25 @@
         <v>6.5</v>
       </c>
       <c r="AA16">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB16">
         <v>2.88</v>
       </c>
       <c r="AC16">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AD16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE16">
         <v>1.3</v>
       </c>
       <c r="AF16">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AG16">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>1.07</v>
+        <v>2.15</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-29 15:00:00</t>
+          <t>2026-10-29 14:30:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.22</v>
+        <v>7.5</v>
       </c>
       <c r="O17">
+        <v>5.75</v>
+      </c>
+      <c r="P17">
+        <v>1.33</v>
+      </c>
+      <c r="Q17">
         <v>6.5</v>
       </c>
-      <c r="P17">
-        <v>10</v>
-      </c>
-      <c r="Q17">
-        <v>1.53</v>
-      </c>
       <c r="R17">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="S17">
+        <v>1.2</v>
+      </c>
+      <c r="T17">
+        <v>4</v>
+      </c>
+      <c r="U17">
+        <v>2</v>
+      </c>
+      <c r="V17">
+        <v>1.71</v>
+      </c>
+      <c r="W17">
         <v>1.17</v>
-      </c>
-      <c r="T17">
-        <v>4.5</v>
-      </c>
-      <c r="U17">
-        <v>1.98</v>
-      </c>
-      <c r="V17">
-        <v>1.77</v>
-      </c>
-      <c r="W17">
-        <v>1.2</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3119,25 +3119,25 @@
         <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB17">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AC17">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AD17">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE17">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.08</v>
       </c>
       <c r="AK17">
-        <v>4.5</v>
+        <v>1.07</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="O18">
-        <v>3.42</v>
+        <v>6.5</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>2.8</v>
+        <v>1.53</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.96</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>1.86</v>
+        <v>2.95</v>
       </c>
       <c r="AC18">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AD18">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AE18">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AF18">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG18">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AK18">
-        <v>1.53</v>
+        <v>4.5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
+        <v>2.3</v>
+      </c>
+      <c r="O19">
+        <v>3.42</v>
+      </c>
+      <c r="P19">
+        <v>2.62</v>
+      </c>
+      <c r="Q19">
+        <v>2.78</v>
+      </c>
+      <c r="R19">
+        <v>2.06</v>
+      </c>
+      <c r="S19">
+        <v>1.39</v>
+      </c>
+      <c r="T19">
+        <v>2.88</v>
+      </c>
+      <c r="U19">
         <v>2.8</v>
       </c>
-      <c r="O19">
-        <v>3.52</v>
-      </c>
-      <c r="P19">
-        <v>2.23</v>
-      </c>
-      <c r="Q19">
-        <v>3.61</v>
-      </c>
-      <c r="R19">
-        <v>2.18</v>
-      </c>
-      <c r="S19">
-        <v>1.34</v>
-      </c>
-      <c r="T19">
-        <v>2.9</v>
-      </c>
-      <c r="U19">
-        <v>2.5</v>
-      </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z19">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA19">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="AB19">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AC19">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="AD19">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE19">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thionville Lusitanos</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q20">
-        <v>2.25</v>
+        <v>3.64</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
         <v>1.08</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.47</v>
+        <v>3.9</v>
       </c>
       <c r="AA20">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB20">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="AC20">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="AD20">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AK20">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-10-29 16:45:00</t>
+          <t>2026-10-29 15:00:00</t>
         </is>
       </c>
     </row>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Thionville Lusitanos</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>3.71</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.67</v>
+        <v>4.2</v>
       </c>
       <c r="Q21">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="U21">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="V21">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>4.35</v>
+        <v>3.47</v>
       </c>
       <c r="AA21">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>2.3</v>
+        <v>1.81</v>
       </c>
       <c r="AC21">
-        <v>2.56</v>
+        <v>3.28</v>
       </c>
       <c r="AD21">
-        <v>1.52</v>
+        <v>1.32</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AG21">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,81 +3895,81 @@
         </is>
       </c>
       <c r="N22">
+        <v>2.2</v>
+      </c>
+      <c r="O22">
+        <v>3.7</v>
+      </c>
+      <c r="P22">
+        <v>3</v>
+      </c>
+      <c r="Q22">
+        <v>2.7</v>
+      </c>
+      <c r="R22">
+        <v>2.3</v>
+      </c>
+      <c r="S22">
+        <v>1.25</v>
+      </c>
+      <c r="T22">
+        <v>3.4</v>
+      </c>
+      <c r="U22">
+        <v>2.3</v>
+      </c>
+      <c r="V22">
+        <v>1.57</v>
+      </c>
+      <c r="W22">
+        <v>1.11</v>
+      </c>
+      <c r="X22">
+        <v>1.01</v>
+      </c>
+      <c r="Y22">
+        <v>1.2</v>
+      </c>
+      <c r="Z22">
+        <v>4.35</v>
+      </c>
+      <c r="AA22">
+        <v>1.64</v>
+      </c>
+      <c r="AB22">
+        <v>2.3</v>
+      </c>
+      <c r="AC22">
+        <v>2.56</v>
+      </c>
+      <c r="AD22">
+        <v>1.52</v>
+      </c>
+      <c r="AE22">
+        <v>1.2</v>
+      </c>
+      <c r="AF22">
+        <v>1.5</v>
+      </c>
+      <c r="AG22">
         <v>2.4</v>
       </c>
-      <c r="O22">
-        <v>2.6</v>
-      </c>
-      <c r="P22">
-        <v>3.1</v>
-      </c>
-      <c r="Q22">
-        <v>3</v>
-      </c>
-      <c r="R22">
-        <v>1.85</v>
-      </c>
-      <c r="S22">
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>1.24</v>
+      </c>
+      <c r="AK22">
         <v>1.57</v>
       </c>
-      <c r="T22">
-        <v>2.19</v>
-      </c>
-      <c r="U22">
-        <v>3.6</v>
-      </c>
-      <c r="V22">
-        <v>1.17</v>
-      </c>
-      <c r="W22">
-        <v>1.02</v>
-      </c>
-      <c r="X22">
-        <v>1.08</v>
-      </c>
-      <c r="Y22">
-        <v>1.52</v>
-      </c>
-      <c r="Z22">
-        <v>2.31</v>
-      </c>
-      <c r="AA22">
-        <v>2.59</v>
-      </c>
-      <c r="AB22">
-        <v>1.39</v>
-      </c>
-      <c r="AC22">
-        <v>5.1</v>
-      </c>
-      <c r="AD22">
-        <v>1.1</v>
-      </c>
-      <c r="AE22">
-        <v>1</v>
-      </c>
-      <c r="AF22">
-        <v>2.14</v>
-      </c>
-      <c r="AG22">
-        <v>1.62</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.35</v>
-      </c>
-      <c r="AK22">
-        <v>1.44</v>
-      </c>
       <c r="AL22">
         <v>0</v>
       </c>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-10-29 17:00:00</t>
+          <t>2026-10-29 16:45:00</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="O23">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="P23">
         <v>2.62</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.79</v>
+        <v>3.51</v>
       </c>
       <c r="O24">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q24">
         <v>4.3</v>
@@ -4260,13 +4260,13 @@
         <v>4.1</v>
       </c>
       <c r="AA24">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AC24">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="AD24">
         <v>1.44</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="Q25">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="R25">
         <v>2.26</v>
@@ -4457,7 +4457,7 @@
         <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="O2">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P2">
         <v>5.25</v>
       </c>
       <c r="Q2">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="R2">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U2">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
         <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
         <v>1.01</v>
       </c>
       <c r="Y2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA2">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB2">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD2">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE2">
         <v>1.11</v>
       </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AK2">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -970,10 +970,10 @@
         <v>4.4</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R4">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="S4">
         <v>1.56</v>
@@ -991,7 +991,7 @@
         <v>1.04</v>
       </c>
       <c r="X4">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y4">
         <v>1.56</v>
@@ -1003,7 +1003,7 @@
         <v>2.7</v>
       </c>
       <c r="AB4">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC4">
         <v>5.75</v>
@@ -1015,10 +1015,10 @@
         <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AG4">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,80 +1124,80 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.48</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="P5">
-        <v>7</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
-        <v>2.09</v>
+        <v>4.74</v>
       </c>
       <c r="R5">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="S5">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="T5">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="V5">
+        <v>1.2</v>
+      </c>
+      <c r="W5">
+        <v>1.03</v>
+      </c>
+      <c r="X5">
+        <v>1.09</v>
+      </c>
+      <c r="Y5">
+        <v>1.6</v>
+      </c>
+      <c r="Z5">
+        <v>2.3</v>
+      </c>
+      <c r="AA5">
+        <v>2.88</v>
+      </c>
+      <c r="AB5">
+        <v>1.4</v>
+      </c>
+      <c r="AC5">
+        <v>6.5</v>
+      </c>
+      <c r="AD5">
+        <v>1.1</v>
+      </c>
+      <c r="AE5">
+        <v>1.02</v>
+      </c>
+      <c r="AF5">
+        <v>2.34</v>
+      </c>
+      <c r="AG5">
+        <v>1.51</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
+        <v>1.33</v>
+      </c>
+      <c r="AK5">
         <v>1.22</v>
-      </c>
-      <c r="W5">
-        <v>1.01</v>
-      </c>
-      <c r="X5">
-        <v>1.07</v>
-      </c>
-      <c r="Y5">
-        <v>1.5</v>
-      </c>
-      <c r="Z5">
-        <v>2.28</v>
-      </c>
-      <c r="AA5">
-        <v>2.62</v>
-      </c>
-      <c r="AB5">
-        <v>1.41</v>
-      </c>
-      <c r="AC5">
-        <v>5.3</v>
-      </c>
-      <c r="AD5">
-        <v>1.09</v>
-      </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
-      <c r="AF5">
-        <v>2.83</v>
-      </c>
-      <c r="AG5">
-        <v>1.34</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.25</v>
-      </c>
-      <c r="AK5">
-        <v>2.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="O6">
-        <v>2.87</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>4.62</v>
+        <v>2.11</v>
       </c>
       <c r="R6">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="S6">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="T6">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="U6">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="V6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y6">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="Z6">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AA6">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AB6">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC6">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AD6">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AE6">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF6">
-        <v>2.22</v>
+        <v>2.83</v>
       </c>
       <c r="AG6">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AK6">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1827,7 +1827,7 @@
         <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AF9">
         <v>1.67</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="P11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q11">
         <v>2.68</v>
@@ -2141,7 +2141,7 @@
         <v>2.74</v>
       </c>
       <c r="AA11">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB11">
         <v>1.6</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="O14">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="P14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -2606,7 +2606,7 @@
         <v>1.85</v>
       </c>
       <c r="S14">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="T14">
         <v>2.22</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O15">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="P15">
         <v>5</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2923,25 +2923,25 @@
         <v>4.2</v>
       </c>
       <c r="P16">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="Q16">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="R16">
-        <v>2.39</v>
+        <v>2.81</v>
       </c>
       <c r="S16">
         <v>1.21</v>
       </c>
       <c r="T16">
-        <v>4.5</v>
+        <v>3.94</v>
       </c>
       <c r="U16">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="V16">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W16">
         <v>1.19</v>
@@ -2956,25 +2956,25 @@
         <v>6.5</v>
       </c>
       <c r="AA16">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AC16">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AD16">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AE16">
         <v>1.3</v>
       </c>
       <c r="AF16">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG16">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>5.75</v>
@@ -3089,25 +3089,25 @@
         <v>1.33</v>
       </c>
       <c r="Q17">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="R17">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S17">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V17">
         <v>1.71</v>
       </c>
       <c r="W17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3125,19 +3125,19 @@
         <v>2.88</v>
       </c>
       <c r="AC17">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD17">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE17">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.08</v>
       </c>
       <c r="AK17">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="O18">
         <v>6.5</v>
@@ -3252,10 +3252,10 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R18">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3282,10 +3282,10 @@
         <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AB18">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AC18">
         <v>1.9</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O19">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="Q19">
         <v>2.78</v>
@@ -3421,7 +3421,7 @@
         <v>2.06</v>
       </c>
       <c r="S19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
         <v>2.88</v>
@@ -3448,7 +3448,7 @@
         <v>1.96</v>
       </c>
       <c r="AB19">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
         <v>3.4</v>
@@ -3463,7 +3463,7 @@
         <v>1.73</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
         <v>2.15</v>
       </c>
       <c r="Q20">
-        <v>3.64</v>
+        <v>3.22</v>
       </c>
       <c r="R20">
         <v>2.16</v>
@@ -3895,10 +3895,10 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="O22">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
         <v>3</v>
@@ -3907,7 +3907,7 @@
         <v>2.7</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3931,10 +3931,10 @@
         <v>1.2</v>
       </c>
       <c r="Z22">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="AA22">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AB22">
         <v>2.3</v>
@@ -3949,7 +3949,7 @@
         <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG22">
         <v>2.4</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK22">
         <v>1.57</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O2">
         <v>3.9</v>
       </c>
       <c r="P2">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q2">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R2">
         <v>2.3</v>
@@ -659,7 +659,7 @@
         <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -671,19 +671,19 @@
         <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB2">
         <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AD2">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
         <v>1.11</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK2">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1462,7 +1462,7 @@
         <v>6.5</v>
       </c>
       <c r="R7">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="S7">
         <v>1.4</v>
@@ -1471,10 +1471,10 @@
         <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W7">
         <v>1.07</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1667,10 +1667,10 @@
         <v>1.3</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         <v>3.41</v>
       </c>
       <c r="P9">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="R9">
         <v>2.08</v>
@@ -1818,7 +1818,7 @@
         <v>1.88</v>
       </c>
       <c r="AB9">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AC9">
         <v>3.25</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
         <v>1.61</v>
@@ -1957,7 +1957,7 @@
         <v>1.39</v>
       </c>
       <c r="T10">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="U10">
         <v>2.71</v>
@@ -1993,7 +1993,7 @@
         <v>1.05</v>
       </c>
       <c r="AF10">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG10">
         <v>1.95</v>
@@ -2268,13 +2268,13 @@
         <v>2.62</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>2.3</v>
       </c>
       <c r="Q12">
-        <v>2.95</v>
+        <v>3.51</v>
       </c>
       <c r="R12">
         <v>2.15</v>
@@ -2283,7 +2283,7 @@
         <v>1.35</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U12">
         <v>2.74</v>
@@ -2295,7 +2295,7 @@
         <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y12">
         <v>1.22</v>
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O13">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P13">
-        <v>7.26</v>
+        <v>6.25</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T13">
         <v>3</v>
@@ -2455,10 +2455,10 @@
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
         <v>1.25</v>
@@ -2467,25 +2467,25 @@
         <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AB13">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD13">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
         <v>2.1</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>4.75</v>
       </c>
       <c r="Q16">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="R16">
         <v>2.81</v>
@@ -2938,10 +2938,10 @@
         <v>3.94</v>
       </c>
       <c r="U16">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="V16">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W16">
         <v>1.19</v>
@@ -2962,16 +2962,16 @@
         <v>3</v>
       </c>
       <c r="AC16">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AD16">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AE16">
         <v>1.3</v>
       </c>
       <c r="AF16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG16">
         <v>2.62</v>
@@ -2990,7 +2990,7 @@
         <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="O17">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="P17">
         <v>1.33</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
         <v>1.03</v>
@@ -3246,7 +3246,7 @@
         <v>1.15</v>
       </c>
       <c r="O18">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>10</v>
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q21">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R21">
         <v>2.15</v>
@@ -3750,7 +3750,7 @@
         <v>1.36</v>
       </c>
       <c r="T21">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="U21">
         <v>2.88</v>
@@ -3768,22 +3768,22 @@
         <v>1.29</v>
       </c>
       <c r="Z21">
-        <v>3.47</v>
+        <v>3.28</v>
       </c>
       <c r="AA21">
         <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="AD21">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AE21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF21">
         <v>1.8</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="O22">
         <v>3.6</v>
@@ -3907,7 +3907,7 @@
         <v>2.7</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK22">
         <v>1.57</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="O23">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="P23">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q23">
         <v>2.71</v>
@@ -4076,13 +4076,13 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="U23">
         <v>2.68</v>
       </c>
       <c r="V23">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4097,13 +4097,13 @@
         <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AC23">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="AD23">
         <v>1.36</v>
@@ -4131,7 +4131,7 @@
         <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.51</v>
+        <v>3.73</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P24">
         <v>1.8</v>
@@ -4242,7 +4242,7 @@
         <v>3.28</v>
       </c>
       <c r="U24">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="V24">
         <v>1.45</v>
@@ -4263,10 +4263,10 @@
         <v>1.74</v>
       </c>
       <c r="AB24">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AD24">
         <v>1.44</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="O25">
         <v>3.4</v>
@@ -4393,7 +4393,7 @@
         <v>2.96</v>
       </c>
       <c r="Q25">
-        <v>2.95</v>
+        <v>2.68</v>
       </c>
       <c r="R25">
         <v>2.26</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
         <v>1.53</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -961,58 +961,58 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="O4">
         <v>2.95</v>
       </c>
       <c r="P4">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="S4">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="T4">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
         <v>1.1</v>
       </c>
       <c r="Y4">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="Z4">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="AA4">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="AB4">
         <v>1.4</v>
       </c>
       <c r="AC4">
-        <v>5.75</v>
+        <v>6.55</v>
       </c>
       <c r="AD4">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
         <v>2.5</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1130,19 +1130,19 @@
         <v>2.75</v>
       </c>
       <c r="P5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>4.74</v>
+        <v>4.2</v>
       </c>
       <c r="R5">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="S5">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="U5">
         <v>4</v>
@@ -1154,16 +1154,16 @@
         <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y5">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA5">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AB5">
         <v>1.4</v>
@@ -1175,13 +1175,13 @@
         <v>1.1</v>
       </c>
       <c r="AE5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF5">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AG5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK5">
         <v>1.22</v>
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="S6">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="T6">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="U6">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="V6">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W6">
         <v>1.03</v>
@@ -1320,31 +1320,31 @@
         <v>1.1</v>
       </c>
       <c r="Y6">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Z6">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="AA6">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AB6">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AD6">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AE6">
         <v>1</v>
       </c>
       <c r="AF6">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AG6">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O9">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="Q9">
         <v>2.47</v>
@@ -1791,7 +1791,7 @@
         <v>2.08</v>
       </c>
       <c r="S9">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T9">
         <v>2.9</v>
@@ -1818,7 +1818,7 @@
         <v>1.88</v>
       </c>
       <c r="AB9">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC9">
         <v>3.25</v>
@@ -1830,7 +1830,7 @@
         <v>1.07</v>
       </c>
       <c r="AF9">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG9">
         <v>2.05</v>
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O10">
         <v>3.1</v>
@@ -2268,7 +2268,7 @@
         <v>2.62</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
         <v>2.3</v>
@@ -2307,7 +2307,7 @@
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>3.04</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
         <v>1.35</v>
@@ -2606,19 +2606,19 @@
         <v>1.85</v>
       </c>
       <c r="S14">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="T14">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="U14">
         <v>3.6</v>
       </c>
       <c r="V14">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
         <v>1.08</v>
@@ -2645,7 +2645,7 @@
         <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AG14">
         <v>1.62</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O15">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P15">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="Q15">
         <v>1.99</v>
@@ -2775,13 +2775,13 @@
         <v>4</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="V15">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2790,28 +2790,28 @@
         <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5.55</v>
+        <v>5.21</v>
       </c>
       <c r="AA15">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB15">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="AC15">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AD15">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="P17">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -3246,10 +3246,10 @@
         <v>1.15</v>
       </c>
       <c r="O18">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q18">
         <v>1.52</v>
@@ -3409,10 +3409,10 @@
         <v>2.37</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Q19">
         <v>2.78</v>
@@ -3421,7 +3421,7 @@
         <v>2.06</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T19">
         <v>2.88</v>
@@ -3460,7 +3460,7 @@
         <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG19">
         <v>2.1</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
         <v>3.22</v>
@@ -3587,13 +3587,13 @@
         <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U20">
         <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W20">
         <v>1.08</v>
@@ -4061,13 +4061,13 @@
         <v>2.45</v>
       </c>
       <c r="O23">
-        <v>3.52</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
         <v>2.75</v>
       </c>
       <c r="Q23">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="R23">
         <v>2.13</v>
@@ -4097,7 +4097,7 @@
         <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
         <v>2.03</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.73</v>
+        <v>3.94</v>
       </c>
       <c r="O24">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="P24">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q24">
         <v>4.3</v>
@@ -4239,10 +4239,10 @@
         <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="U24">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="V24">
         <v>1.45</v>
@@ -4254,25 +4254,25 @@
         <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA24">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC24">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AD24">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AE24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
         <v>1.65</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="AK24">
         <v>1.22</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="O25">
         <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
         <v>2.68</v>
       </c>
       <c r="R25">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S25">
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="U25">
         <v>2.62</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
         <v>1.53</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O2">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P2">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q2">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
         <v>1.29</v>
@@ -656,10 +656,10 @@
         <v>3.3</v>
       </c>
       <c r="U2">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
         <v>1.07</v>
@@ -674,13 +674,13 @@
         <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB2">
         <v>1.98</v>
       </c>
       <c r="AC2">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
         <v>1.36</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK2">
         <v>2.5</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O5">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R5">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="S5">
         <v>1.67</v>
       </c>
       <c r="T5">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="U5">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
         <v>1.11</v>
@@ -1166,7 +1166,7 @@
         <v>3</v>
       </c>
       <c r="AB5">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC5">
         <v>6.5</v>
@@ -1175,7 +1175,7 @@
         <v>1.1</v>
       </c>
       <c r="AE5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF5">
         <v>2.45</v>
@@ -1197,7 +1197,7 @@
         <v>1.35</v>
       </c>
       <c r="AK5">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1293,7 +1293,7 @@
         <v>3.4</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>7.25</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
@@ -1326,7 +1326,7 @@
         <v>2.12</v>
       </c>
       <c r="AA6">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB6">
         <v>1.35</v>
@@ -1785,10 +1785,10 @@
         <v>3.28</v>
       </c>
       <c r="Q9">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S9">
         <v>1.35</v>
@@ -1815,25 +1815,25 @@
         <v>3.38</v>
       </c>
       <c r="AA9">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB9">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC9">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="AD9">
         <v>1.3</v>
       </c>
       <c r="AE9">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF9">
         <v>1.7</v>
       </c>
       <c r="AG9">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O10">
         <v>3.1</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Q10">
         <v>2.99</v>
@@ -1960,7 +1960,7 @@
         <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="V10">
         <v>1.35</v>
@@ -2111,34 +2111,34 @@
         <v>3.4</v>
       </c>
       <c r="Q11">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="R11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="T11">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V11">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
         <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z11">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AA11">
         <v>2.15</v>
@@ -2147,19 +2147,19 @@
         <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AD11">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE11">
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
         <v>3.3</v>
       </c>
       <c r="P12">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q12">
-        <v>3.51</v>
+        <v>3.53</v>
       </c>
       <c r="R12">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2286,7 +2286,7 @@
         <v>3.1</v>
       </c>
       <c r="U12">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
         <v>1.46</v>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
         <v>4.1</v>
@@ -2310,7 +2310,7 @@
         <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="AD12">
         <v>1.37</v>
@@ -2338,7 +2338,7 @@
         <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>1.53</v>
       </c>
       <c r="T14">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="U14">
         <v>3.6</v>
@@ -2621,7 +2621,7 @@
         <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y14">
         <v>1.53</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AK14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="O15">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P15">
         <v>5.75</v>
       </c>
       <c r="Q15">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="R15">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U15">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V15">
         <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="AA15">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AB15">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="AC15">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AD15">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG15">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.13</v>
       </c>
       <c r="AK15">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,34 +2917,34 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="O16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P16">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="R16">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T16">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="U16">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V16">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="W16">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X16">
         <v>1.01</v>
@@ -2962,16 +2962,16 @@
         <v>3</v>
       </c>
       <c r="AC16">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AD16">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AE16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG16">
         <v>2.62</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3083,10 +3083,10 @@
         <v>8</v>
       </c>
       <c r="O17">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="P17">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Q17">
         <v>7.5</v>
@@ -3131,7 +3131,7 @@
         <v>1.8</v>
       </c>
       <c r="AE17">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AF17">
         <v>1.65</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="O18">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="P18">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R18">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3264,13 +3264,13 @@
         <v>4.5</v>
       </c>
       <c r="U18">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="V18">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,19 +3282,19 @@
         <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AB18">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="AC18">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AD18">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AE18">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF18">
         <v>1.75</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK18">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3409,22 +3409,22 @@
         <v>2.37</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
         <v>2.7</v>
       </c>
       <c r="Q19">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R19">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="S19">
         <v>1.39</v>
       </c>
       <c r="T19">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="U19">
         <v>2.8</v>
@@ -3445,7 +3445,7 @@
         <v>3.5</v>
       </c>
       <c r="AA19">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AB19">
         <v>1.8</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q20">
-        <v>3.22</v>
+        <v>3.31</v>
       </c>
       <c r="R20">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S20">
         <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
         <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
         <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AB20">
         <v>2.04</v>
       </c>
       <c r="AC20">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="AD20">
         <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
         <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>3.6</v>
       </c>
       <c r="P22">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3913,7 +3913,7 @@
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U22">
         <v>2.3</v>
@@ -3922,37 +3922,37 @@
         <v>1.57</v>
       </c>
       <c r="W22">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z22">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AA22">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB22">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AC22">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AD22">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE22">
         <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG22">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O23">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q23">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4097,10 +4097,10 @@
         <v>4.1</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB23">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC23">
         <v>3.01</v>
@@ -4109,7 +4109,7 @@
         <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
         <v>1.6</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK23">
         <v>1.57</v>
@@ -4224,61 +4224,61 @@
         <v>3.94</v>
       </c>
       <c r="O24">
-        <v>3.78</v>
+        <v>3.65</v>
       </c>
       <c r="P24">
         <v>1.85</v>
       </c>
       <c r="Q24">
-        <v>4.3</v>
+        <v>4.64</v>
       </c>
       <c r="R24">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="U24">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="V24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA24">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AB24">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC24">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
         <v>1.65</v>
       </c>
       <c r="AG24">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AK24">
         <v>1.22</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P25">
         <v>2.8</v>
       </c>
       <c r="Q25">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="R25">
         <v>2.28</v>
@@ -4420,7 +4420,7 @@
         <v>1.29</v>
       </c>
       <c r="Z25">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
         <v>1.9</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -635,28 +635,28 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O2">
         <v>4</v>
       </c>
       <c r="P2">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q2">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="R2">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="S2">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T2">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U2">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
         <v>1.44</v>
@@ -665,35 +665,35 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z2">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA2">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AB2">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AC2">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AD2">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
         <v>1.11</v>
       </c>
       <c r="AF2">
+        <v>1.91</v>
+      </c>
+      <c r="AG2">
         <v>1.75</v>
       </c>
-      <c r="AG2">
-        <v>1.91</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK2">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q3">
         <v>5.7</v>
@@ -825,10 +825,10 @@
         <v>1.24</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y3">
         <v>1.43</v>
@@ -843,10 +843,10 @@
         <v>1.45</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE3">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1939,37 +1939,37 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O10">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q10">
-        <v>2.99</v>
+        <v>3.38</v>
       </c>
       <c r="R10">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S10">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="T10">
         <v>2.8</v>
       </c>
       <c r="U10">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y10">
         <v>1.33</v>
@@ -1978,16 +1978,16 @@
         <v>3.25</v>
       </c>
       <c r="AA10">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AB10">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC10">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="AD10">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
         <v>1.05</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P11">
         <v>3.4</v>
@@ -2117,19 +2117,19 @@
         <v>2</v>
       </c>
       <c r="S11">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="T11">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="U11">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V11">
         <v>1.3</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2138,7 +2138,7 @@
         <v>1.4</v>
       </c>
       <c r="Z11">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA11">
         <v>2.15</v>
@@ -2156,10 +2156,10 @@
         <v>1.03</v>
       </c>
       <c r="AF11">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG11">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,22 +2265,22 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q12">
-        <v>3.53</v>
+        <v>3.57</v>
       </c>
       <c r="R12">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T12">
         <v>3.1</v>
@@ -2289,40 +2289,40 @@
         <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
         <v>1.85</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="AD12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
         <v>1.4</v>
@@ -2609,7 +2609,7 @@
         <v>1.53</v>
       </c>
       <c r="T14">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U14">
         <v>3.6</v>
@@ -2621,13 +2621,13 @@
         <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y14">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z14">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AA14">
         <v>2.62</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O15">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="P15">
         <v>5.75</v>
@@ -2775,7 +2775,7 @@
         <v>3.8</v>
       </c>
       <c r="U15">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
         <v>1.62</v>
@@ -2790,16 +2790,16 @@
         <v>1.14</v>
       </c>
       <c r="Z15">
-        <v>5.15</v>
+        <v>5.22</v>
       </c>
       <c r="AA15">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AB15">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="AC15">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="AD15">
         <v>1.56</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK15">
         <v>2.63</v>
@@ -2923,10 +2923,10 @@
         <v>4.1</v>
       </c>
       <c r="P16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q16">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="R16">
         <v>2.5</v>
@@ -2956,10 +2956,10 @@
         <v>6.5</v>
       </c>
       <c r="AA16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB16">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AC16">
         <v>2.04</v>
@@ -2971,10 +2971,10 @@
         <v>1.33</v>
       </c>
       <c r="AF16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG16">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>8</v>
+        <v>1.19</v>
       </c>
       <c r="O17">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="P17">
-        <v>1.33</v>
+        <v>11</v>
       </c>
       <c r="Q17">
-        <v>7.5</v>
+        <v>1.53</v>
       </c>
       <c r="R17">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="S17">
         <v>1.17</v>
@@ -3101,13 +3101,13 @@
         <v>4.5</v>
       </c>
       <c r="U17">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="V17">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X17">
         <v>1.01</v>
@@ -3119,25 +3119,25 @@
         <v>6.5</v>
       </c>
       <c r="AA17">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB17">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="AC17">
         <v>2</v>
       </c>
       <c r="AD17">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AE17">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.19</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="P18">
-        <v>11</v>
+        <v>1.33</v>
       </c>
       <c r="Q18">
-        <v>1.53</v>
+        <v>7.5</v>
       </c>
       <c r="R18">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3264,13 +3264,13 @@
         <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V18">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3282,25 +3282,25 @@
         <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB18">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AC18">
         <v>2</v>
       </c>
       <c r="AD18">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE18">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG18">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,28 +3406,28 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O19">
         <v>3.1</v>
       </c>
       <c r="P19">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q19">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="R19">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="S19">
         <v>1.39</v>
       </c>
       <c r="T19">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="V19">
         <v>1.4</v>
@@ -3445,10 +3445,10 @@
         <v>3.5</v>
       </c>
       <c r="AA19">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC19">
         <v>3.4</v>
@@ -3463,7 +3463,7 @@
         <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="O20">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P20">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q20">
-        <v>3.31</v>
+        <v>3.36</v>
       </c>
       <c r="R20">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="S20">
         <v>1.3</v>
@@ -3599,7 +3599,7 @@
         <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.22</v>
@@ -3620,13 +3620,13 @@
         <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF20">
         <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AK20">
         <v>1.36</v>
@@ -3898,16 +3898,16 @@
         <v>2.31</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
         <v>1.25</v>
@@ -3916,10 +3916,10 @@
         <v>3.6</v>
       </c>
       <c r="U22">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V22">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W22">
         <v>1.13</v>
@@ -3928,31 +3928,31 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA22">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
         <v>2.37</v>
       </c>
       <c r="AC22">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD22">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AE22">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF22">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG22">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK22">
         <v>1.57</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q23">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="R23">
         <v>2.16</v>
@@ -4076,13 +4076,13 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="U23">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="V23">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4094,16 +4094,16 @@
         <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA23">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AC23">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="AD23">
         <v>1.36</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>1.85</v>
       </c>
       <c r="Q24">
-        <v>4.64</v>
+        <v>4.67</v>
       </c>
       <c r="R24">
         <v>2.37</v>
@@ -4239,10 +4239,10 @@
         <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="V24">
         <v>1.44</v>
@@ -4254,16 +4254,16 @@
         <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA24">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC24">
         <v>3.1</v>
@@ -4275,7 +4275,7 @@
         <v>1.1</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
         <v>2.05</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="O25">
         <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="Q25">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R25">
         <v>2.28</v>
@@ -4420,7 +4420,7 @@
         <v>1.29</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA25">
         <v>1.9</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
         <v>1.57</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "65"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1", "90"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G4">
@@ -957,32 +957,32 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
-        <v>1.75</v>
+        <v>3.3</v>
       </c>
       <c r="O4">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="P4">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S4">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="U4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="V4">
         <v>1.17</v>
@@ -991,34 +991,34 @@
         <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y4">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="Z4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AA4">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="AB4">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC4">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="AD4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG4">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AK4">
-        <v>1.88</v>
+        <v>1.29</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1092,22 +1092,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1120,111 +1120,111 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="O5">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="P5">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q5">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R5">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="S5">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="T5">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="V5">
         <v>1.17</v>
       </c>
       <c r="W5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y5">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Z5">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AA5">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AB5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC5">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="AD5">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AE5">
         <v>1.02</v>
       </c>
       <c r="AF5">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AG5">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
+          <t>["27"]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ5">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AK5">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1279,11 +1279,11 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1293,67 +1293,67 @@
         <v>3.4</v>
       </c>
       <c r="P6">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S6">
         <v>1.57</v>
       </c>
       <c r="T6">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="U6">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="V6">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y6">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Z6">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="AA6">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AB6">
         <v>1.35</v>
       </c>
       <c r="AC6">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AD6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE6">
         <v>1</v>
       </c>
       <c r="AF6">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AG6">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27", "30", "37"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58", "82"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1446,23 +1446,23 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>3.66</v>
+        <v>3.74</v>
       </c>
       <c r="P7">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q7">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S7">
         <v>1.4</v>
@@ -1489,25 +1489,25 @@
         <v>2.97</v>
       </c>
       <c r="AA7">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AB7">
         <v>1.68</v>
       </c>
       <c r="AC7">
-        <v>3.77</v>
+        <v>3.94</v>
       </c>
       <c r="AD7">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF7">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG7">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1516,11 +1516,11 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK7">
         <v>1.05</v>
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P9">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="Q9">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="R9">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U9">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AB9">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC9">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="AD9">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AE9">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG9">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2428,22 +2428,22 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="O13">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="Q13">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="R13">
         <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T13">
         <v>3</v>
@@ -2455,37 +2455,37 @@
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA13">
+        <v>1.9</v>
+      </c>
+      <c r="AB13">
         <v>1.87</v>
       </c>
-      <c r="AB13">
-        <v>1.9</v>
-      </c>
       <c r="AC13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE13">
         <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.08</v>
       </c>
       <c r="AK13">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2917,55 +2917,55 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O16">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="P16">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S16">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T16">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V16">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="W16">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z16">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB16">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC16">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AD16">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AE16">
         <v>1.33</v>
@@ -2990,7 +2990,7 @@
         <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,28 +3080,28 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="O17">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>11</v>
+        <v>9.9</v>
       </c>
       <c r="Q17">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="S17">
         <v>1.17</v>
       </c>
       <c r="T17">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U17">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="V17">
         <v>1.69</v>
@@ -3125,19 +3125,19 @@
         <v>2.66</v>
       </c>
       <c r="AC17">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD17">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE17">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="O18">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="P18">
         <v>1.33</v>
       </c>
       <c r="Q18">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>2.75</v>
@@ -3264,13 +3264,13 @@
         <v>4.5</v>
       </c>
       <c r="U18">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V18">
         <v>1.71</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3288,13 +3288,13 @@
         <v>2.88</v>
       </c>
       <c r="AC18">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE18">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF18">
         <v>1.65</v>
@@ -3316,7 +3316,7 @@
         <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3735,55 +3735,55 @@
         <v>1.67</v>
       </c>
       <c r="O21">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P21">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q21">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R21">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T21">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="U21">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="V21">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W21">
         <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="AA21">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB21">
         <v>1.9</v>
       </c>
       <c r="AC21">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="AD21">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF21">
         <v>1.8</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3898,10 +3898,10 @@
         <v>2.31</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P22">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="Q22">
         <v>2.7</v>
@@ -3910,49 +3910,49 @@
         <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
         <v>3.6</v>
       </c>
       <c r="U22">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>4.8</v>
+        <v>5.17</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB22">
-        <v>2.37</v>
+        <v>2.75</v>
       </c>
       <c r="AC22">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="AD22">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF22">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG22">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AK22">
         <v>1.57</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "47", "73", "75"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["39", "45"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "50"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2261,35 +2261,35 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
         <v>2.9</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P12">
         <v>2.25</v>
       </c>
       <c r="Q12">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="R12">
         <v>2.15</v>
       </c>
       <c r="S12">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T12">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2298,74 +2298,74 @@
         <v>1.01</v>
       </c>
       <c r="Y12">
+        <v>1.29</v>
+      </c>
+      <c r="Z12">
+        <v>3.3</v>
+      </c>
+      <c r="AA12">
+        <v>2</v>
+      </c>
+      <c r="AB12">
+        <v>1.82</v>
+      </c>
+      <c r="AC12">
+        <v>3.34</v>
+      </c>
+      <c r="AD12">
+        <v>1.32</v>
+      </c>
+      <c r="AE12">
+        <v>1.06</v>
+      </c>
+      <c r="AF12">
+        <v>1.74</v>
+      </c>
+      <c r="AG12">
+        <v>2</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.25</v>
       </c>
-      <c r="Z12">
-        <v>3.8</v>
-      </c>
-      <c r="AA12">
-        <v>1.85</v>
-      </c>
-      <c r="AB12">
-        <v>1.89</v>
-      </c>
-      <c r="AC12">
-        <v>3.18</v>
-      </c>
-      <c r="AD12">
-        <v>1.35</v>
-      </c>
-      <c r="AE12">
-        <v>1.1</v>
-      </c>
-      <c r="AF12">
-        <v>1.67</v>
-      </c>
-      <c r="AG12">
-        <v>2.1</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.24</v>
-      </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2434,16 +2434,16 @@
         <v>4</v>
       </c>
       <c r="P13">
-        <v>6.67</v>
+        <v>6.72</v>
       </c>
       <c r="Q13">
         <v>1.91</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T13">
         <v>3</v>
@@ -2455,50 +2455,50 @@
         <v>1.44</v>
       </c>
       <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.25</v>
+      </c>
+      <c r="Z13">
+        <v>3.6</v>
+      </c>
+      <c r="AA13">
+        <v>1.86</v>
+      </c>
+      <c r="AB13">
+        <v>1.81</v>
+      </c>
+      <c r="AC13">
+        <v>3.3</v>
+      </c>
+      <c r="AD13">
+        <v>1.29</v>
+      </c>
+      <c r="AE13">
         <v>1.08</v>
       </c>
-      <c r="X13">
+      <c r="AF13">
+        <v>1.95</v>
+      </c>
+      <c r="AG13">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>["11", "58"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>["38"]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.29</v>
-      </c>
-      <c r="Z13">
-        <v>3.5</v>
-      </c>
-      <c r="AA13">
-        <v>1.9</v>
-      </c>
-      <c r="AB13">
-        <v>1.87</v>
-      </c>
-      <c r="AC13">
-        <v>3.4</v>
-      </c>
-      <c r="AD13">
-        <v>1.3</v>
-      </c>
-      <c r="AE13">
-        <v>1.1</v>
-      </c>
-      <c r="AF13">
-        <v>2.05</v>
-      </c>
-      <c r="AG13">
-        <v>1.8</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.08</v>
       </c>
       <c r="AK13">
         <v>2.42</v>
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2587,20 +2587,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="O14">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="P14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R14">
         <v>1.85</v>
@@ -2609,10 +2609,10 @@
         <v>1.53</v>
       </c>
       <c r="T14">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="U14">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="V14">
         <v>1.22</v>
@@ -2624,16 +2624,16 @@
         <v>1.11</v>
       </c>
       <c r="Y14">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z14">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AA14">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AB14">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC14">
         <v>5.75</v>
@@ -2645,10 +2645,10 @@
         <v>1.01</v>
       </c>
       <c r="AF14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AG14">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,37 +2661,37 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2712,149 +2712,149 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="O15">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="P15">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="R15">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S15">
+        <v>1.17</v>
+      </c>
+      <c r="T15">
+        <v>4.6</v>
+      </c>
+      <c r="U15">
+        <v>1.91</v>
+      </c>
+      <c r="V15">
+        <v>1.89</v>
+      </c>
+      <c r="W15">
         <v>1.22</v>
-      </c>
-      <c r="T15">
-        <v>3.8</v>
-      </c>
-      <c r="U15">
-        <v>2.16</v>
-      </c>
-      <c r="V15">
-        <v>1.62</v>
-      </c>
-      <c r="W15">
-        <v>1.15</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>5.22</v>
+        <v>7</v>
       </c>
       <c r="AA15">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AB15">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="AC15">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="AD15">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AE15">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AF15">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["25", "45+1", "59", "72", "90+4"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ15">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2870,27 +2870,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,81 +2917,81 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="O16">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="P16">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="Q16">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="R16">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="S16">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="U16">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="V16">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AA16">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AB16">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC16">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AD16">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AE16">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF16">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG16">
+        <v>2.1</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.14</v>
+      </c>
+      <c r="AK16">
         <v>2.8</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.2</v>
-      </c>
-      <c r="AK16">
-        <v>2.25</v>
-      </c>
       <c r="AL16">
         <v>0</v>
       </c>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-10-29 14:30:00</t>
+          <t>2026-10-29 14:45:00</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.21</v>
+        <v>8.6</v>
       </c>
       <c r="O17">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="P17">
-        <v>9.9</v>
+        <v>1.29</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>7.5</v>
       </c>
       <c r="R17">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="S17">
         <v>1.17</v>
       </c>
       <c r="T17">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U17">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="V17">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W17">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X17">
         <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z17">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA17">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB17">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="AC17">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE17">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>7.75</v>
+        <v>1.14</v>
       </c>
       <c r="O18">
-        <v>5.5</v>
+        <v>6.9</v>
       </c>
       <c r="P18">
-        <v>1.33</v>
+        <v>12</v>
       </c>
       <c r="Q18">
-        <v>7</v>
+        <v>1.52</v>
       </c>
       <c r="R18">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="S18">
         <v>1.17</v>
@@ -3264,43 +3264,43 @@
         <v>4.5</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V18">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AC18">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AD18">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AE18">
         <v>1.3</v>
       </c>
       <c r="AF18">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK18">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O19">
         <v>3.1</v>
@@ -3415,7 +3415,7 @@
         <v>2.8</v>
       </c>
       <c r="Q19">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="R19">
         <v>2.12</v>
@@ -3436,34 +3436,34 @@
         <v>1.06</v>
       </c>
       <c r="X19">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z19">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA19">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB19">
         <v>1.81</v>
       </c>
       <c r="AC19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
         <v>1.7</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P20">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q20">
         <v>3.36</v>
       </c>
       <c r="R20">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="S20">
         <v>1.3</v>
@@ -3599,34 +3599,34 @@
         <v>1.07</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB20">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AC20">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
         <v>1.62</v>
       </c>
       <c r="AG20">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AK20">
         <v>1.36</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P23">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q23">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="R23">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S23">
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="U23">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="V23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="AB23">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="AC23">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="AD23">
         <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
         <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>1.85</v>
       </c>
       <c r="Q24">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="R24">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="S24">
         <v>1.33</v>
@@ -4242,13 +4242,13 @@
         <v>3.3</v>
       </c>
       <c r="U24">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V24">
         <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1</v>
@@ -4257,13 +4257,13 @@
         <v>1.27</v>
       </c>
       <c r="Z24">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB24">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AC24">
         <v>3.1</v>
@@ -4272,10 +4272,10 @@
         <v>1.4</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF24">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG24">
         <v>2.05</v>
@@ -4390,19 +4390,19 @@
         <v>3.3</v>
       </c>
       <c r="P25">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="Q25">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="R25">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S25">
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="U25">
         <v>2.62</v>
@@ -4411,13 +4411,13 @@
         <v>1.4</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
         <v>3.6</v>
@@ -4426,7 +4426,7 @@
         <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AC25">
         <v>3.25</v>
@@ -4438,7 +4438,7 @@
         <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
         <v>2.1</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-10-29.xlsx
+++ b/jogos_2026-10-29.xlsx
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "51"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3060,23 +3060,23 @@
         <v>0</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "37", "56", "67", "87", "89"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["24", "38", "66", "72", "81"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["16", "45+2", "90+4"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3374,139 +3374,139 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="R19">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U19">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W19">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z19">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA19">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AB19">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AC19">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="AD19">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
         <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "49"]</t>
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="AK19">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3537,19 +3537,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3561,69 +3561,69 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="O20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P20">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q20">
-        <v>3.36</v>
+        <v>2.75</v>
       </c>
       <c r="R20">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA20">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AB20">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="AC20">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF20">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG20">
         <v>2.2</v>
@@ -3635,41 +3635,41 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84"]</t>
         </is>
       </c>
       <c r="AJ20">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3709,26 +3709,26 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3741,98 +3741,98 @@
         <v>4.2</v>
       </c>
       <c r="Q21">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="R21">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S21">
         <v>1.33</v>
       </c>
       <c r="T21">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U21">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="V21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W21">
         <v>1.08</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
         <v>1.25</v>
       </c>
       <c r="Z21">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA21">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AB21">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AC21">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD21">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF21">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG21">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["36"]</t>
         </is>
       </c>
       <c r="AJ21">
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -3872,26 +3872,26 @@
         </is>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N22">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "61"]</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "74"]</t>
         </is>
       </c>
       <c r="AJ22">
@@ -3974,28 +3974,28 @@
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>26</v>
       </c>
       <c r="AP22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.71</v>
+        <v>2.42</v>
       </c>
       <c r="O23">
         <v>3.45</v>
@@ -4079,43 +4079,43 @@
         <v>3.34</v>
       </c>
       <c r="U23">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="V23">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
         <v>4.5</v>
       </c>
       <c r="AA23">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AB23">
         <v>2.17</v>
       </c>
       <c r="AC23">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE23">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG23">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="N24">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="O24">
         <v>3.65</v>
@@ -4230,7 +4230,7 @@
         <v>1.85</v>
       </c>
       <c r="Q24">
-        <v>4.71</v>
+        <v>4.74</v>
       </c>
       <c r="R24">
         <v>2.36</v>
@@ -4239,37 +4239,37 @@
         <v>1.33</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V24">
         <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X24">
         <v>1</v>
       </c>
       <c r="Y24">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z24">
         <v>3.6</v>
       </c>
       <c r="AA24">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB24">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC24">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
         <v>1.08</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="Q25">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="R25">
         <v>2.29</v>
@@ -4402,7 +4402,7 @@
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U25">
         <v>2.62</v>
@@ -4435,7 +4435,7 @@
         <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF25">
         <v>1.65</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AL25">
         <v>0</v>
